--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE675BA8-531C-4A65-A935-D18296C6C877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0157CC-2C6F-4249-A7B4-D1FAE6635D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="218">
   <si>
     <t>variable</t>
   </si>
@@ -289,39 +289,21 @@
     <t>date_electoral_sub_leg</t>
   </si>
   <si>
-    <t>Date of the subnational legislative election</t>
-  </si>
-  <si>
     <t>voters_registered_sub_leg</t>
   </si>
   <si>
-    <t>Total registered voters for subnational legislative elections</t>
-  </si>
-  <si>
     <t>total_voters_sub_leg</t>
   </si>
   <si>
-    <t>Total votes cast in subnational legislative elections</t>
-  </si>
-  <si>
     <t>perc_voters_sub_leg</t>
   </si>
   <si>
-    <t>Proportion of registered voters who voted in legislative elections</t>
-  </si>
-  <si>
     <t>valid_votes_sub_leg</t>
   </si>
   <si>
-    <t>Total valid votes in subnational legislative elections</t>
-  </si>
-  <si>
     <t>perc_valid_votes_sub_leg</t>
   </si>
   <si>
-    <t>Percentage of valid votes in legislative elections</t>
-  </si>
-  <si>
     <t>party_name_sub_leg</t>
   </si>
   <si>
@@ -355,30 +337,18 @@
     <t>margin_victory_sub_leg</t>
   </si>
   <si>
-    <t>Difference in vote share between the winner and second-place party (v1 - v2)</t>
-  </si>
-  <si>
     <t>#90A4AE,#00E5FF</t>
   </si>
   <si>
     <t>cumulative_electoral_year_sub_leg</t>
   </si>
   <si>
-    <t>Cumulative count of subnational legislative elections in the state</t>
-  </si>
-  <si>
     <t>concurrent_election_with_nat_sub_leg</t>
   </si>
   <si>
-    <t>Whether subnational legislative and national elections occurred concurrently (1 = Yes, 0 = No)</t>
-  </si>
-  <si>
     <t>num_parties_election_contest_sub_leg</t>
   </si>
   <si>
-    <t>Number of parties contesting subnational legislative elections</t>
-  </si>
-  <si>
     <t>total_seats_in_contest_sub_leg</t>
   </si>
   <si>
@@ -394,21 +364,12 @@
     <t>num_seats_opos_sub_leg</t>
   </si>
   <si>
-    <t>Seats controlled by opposition parties in the subnational legislature</t>
-  </si>
-  <si>
     <t>perc_seats_opos_sub_leg</t>
   </si>
   <si>
-    <t>Percentage of seats controlled by opposition parties</t>
-  </si>
-  <si>
     <t>chamber_sub_leg</t>
   </si>
   <si>
-    <t>Number of chambers in the subnational legislature (1 = Unicameral, 2 = Bicameral)</t>
-  </si>
-  <si>
     <t>#d73027,#4575b4</t>
   </si>
   <si>
@@ -424,9 +385,6 @@
     <t>enp_leg_sub_leg</t>
   </si>
   <si>
-    <t>Effective number of legislative parties in elections (Laakso and Taagepera)</t>
-  </si>
-  <si>
     <t>dataset</t>
   </si>
   <si>
@@ -685,12 +643,6 @@
     <t>Effective number of parties competing in election</t>
   </si>
   <si>
-    <t>Seats controlled by the governor's party in the subnational legislature</t>
-  </si>
-  <si>
-    <t>Percentage of seats controlled by the governor's party</t>
-  </si>
-  <si>
     <t>Voter Turnout Percentage</t>
   </si>
   <si>
@@ -722,6 +674,9 @@
   </si>
   <si>
     <t>Difference in vote percentage between winner and runner-up</t>
+  </si>
+  <si>
+    <t>#C5CA8A,#5E304F,#5FBFF9</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1024,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1098,7 +1052,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1116,7 +1070,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1124,7 +1078,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1142,7 +1096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1150,7 +1104,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1168,7 +1122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1176,7 +1130,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1194,7 +1148,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1202,7 +1156,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1220,15 +1174,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -1254,10 +1208,10 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -1281,15 +1235,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -1310,15 +1264,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -1342,15 +1296,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -1374,15 +1328,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -1406,15 +1360,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -1435,15 +1389,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -1467,15 +1421,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -1499,15 +1453,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="B15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -1533,10 +1487,10 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -1548,7 +1502,7 @@
         <v>28</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>217</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1560,15 +1514,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -1589,15 +1543,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -1621,15 +1575,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -1653,15 +1607,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -1685,15 +1639,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D21" t="s">
         <v>49</v>
@@ -1717,15 +1671,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D22" t="s">
         <v>49</v>
@@ -1749,15 +1703,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -1781,15 +1735,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -1810,15 +1764,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -1842,15 +1796,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -1874,15 +1828,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -1906,15 +1860,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -1938,15 +1892,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D29" t="s">
         <v>49</v>
@@ -1970,47 +1924,47 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B30" t="s">
-        <v>160</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="B30" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
@@ -2034,15 +1988,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
@@ -2066,15 +2020,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D33" t="s">
         <v>49</v>
@@ -2098,15 +2052,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D34" t="s">
         <v>49</v>
@@ -2127,15 +2081,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D35" t="s">
         <v>49</v>
@@ -2159,15 +2113,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D36" t="s">
         <v>49</v>
@@ -2191,15 +2145,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="D37" t="s">
         <v>49</v>
@@ -2223,15 +2177,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D38" t="s">
         <v>49</v>
@@ -2255,15 +2209,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D39" t="s">
         <v>49</v>
@@ -2287,15 +2241,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>72</v>
       </c>
       <c r="B40" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D40" t="s">
         <v>49</v>
@@ -2319,15 +2273,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>49</v>
@@ -2351,15 +2305,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D42" t="s">
         <v>49</v>
@@ -2383,15 +2337,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="D43" t="s">
         <v>49</v>
@@ -2415,15 +2369,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D44" t="s">
         <v>49</v>
@@ -2447,15 +2401,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="D45" t="s">
         <v>49</v>
@@ -2479,15 +2433,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>78</v>
       </c>
       <c r="B46" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D46" t="s">
         <v>49</v>
@@ -2511,15 +2465,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>79</v>
       </c>
       <c r="B47" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="D47" t="s">
         <v>49</v>
@@ -2543,15 +2497,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D48" t="s">
         <v>49</v>
@@ -2575,15 +2529,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>81</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D49" t="s">
         <v>49</v>
@@ -2607,15 +2561,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D50" t="s">
         <v>49</v>
@@ -2639,7 +2593,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>84</v>
       </c>
@@ -2650,13 +2604,10 @@
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>87</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D52" t="s">
         <v>49</v>
       </c>
@@ -2673,12 +2624,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>89</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D53" t="s">
         <v>49</v>
@@ -2696,12 +2644,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D54" t="s">
         <v>49</v>
@@ -2719,12 +2664,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>93</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
         <v>49</v>
@@ -2745,12 +2687,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D56" t="s">
         <v>49</v>
@@ -2768,12 +2707,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>97</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D57" t="s">
         <v>49</v>
@@ -2794,9 +2730,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D58" t="s">
         <v>49</v>
@@ -2805,9 +2741,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D59" t="s">
         <v>49</v>
@@ -2816,9 +2752,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D60" t="s">
         <v>49</v>
@@ -2827,9 +2763,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D61" t="s">
         <v>49</v>
@@ -2838,9 +2774,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D62" t="s">
         <v>49</v>
@@ -2849,9 +2785,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D63" t="s">
         <v>49</v>
@@ -2860,9 +2796,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D64" t="s">
         <v>49</v>
@@ -2871,9 +2807,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D65" t="s">
         <v>49</v>
@@ -2882,9 +2818,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D66" t="s">
         <v>49</v>
@@ -2893,9 +2829,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D67" t="s">
         <v>49</v>
@@ -2904,12 +2840,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>109</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D68" t="s">
         <v>49</v>
@@ -2927,12 +2860,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>112</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D69" t="s">
         <v>49</v>
@@ -2950,12 +2880,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>114</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D70" t="s">
         <v>49</v>
@@ -2964,7 +2891,7 @@
         <v>86</v>
       </c>
       <c r="G70" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -2976,12 +2903,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>116</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D71" t="s">
         <v>49</v>
@@ -2999,9 +2923,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D72" t="s">
         <v>49</v>
@@ -3010,9 +2934,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D73" t="s">
         <v>49</v>
@@ -3021,12 +2945,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>120</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="D74" t="s">
         <v>49</v>
@@ -3044,12 +2965,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>121</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="D75" t="s">
         <v>49</v>
@@ -3070,12 +2988,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>122</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
         <v>49</v>
@@ -3093,12 +3008,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>124</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D77" t="s">
         <v>49</v>
@@ -3119,12 +3031,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>126</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D78" t="s">
         <v>49</v>
@@ -3133,7 +3042,7 @@
         <v>86</v>
       </c>
       <c r="G78" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -3145,9 +3054,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D79" t="s">
         <v>49</v>
@@ -3156,9 +3065,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D80" t="s">
         <v>49</v>
@@ -3167,9 +3076,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D81" t="s">
         <v>49</v>
@@ -3178,12 +3087,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>132</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D82" t="s">
         <v>49</v>
@@ -3202,13 +3108,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J82" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="gender"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J82" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0157CC-2C6F-4249-A7B4-D1FAE6635D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEB0549-3326-408F-B1EB-371EFB2609C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2296,10 +2296,10 @@
         <v>69</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>20</v>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEB0549-3326-408F-B1EB-371EFB2609C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DCB26F-CA0E-4B5A-846E-CBDF9B846734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1025,20 +1025,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="84.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="84.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -1892,8 +1892,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B29" t="s">
@@ -1915,7 +1915,7 @@
         <v>36</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1924,7 +1924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>63</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>64</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>70</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>72</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>73</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>75</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>76</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>77</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>78</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>79</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>80</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>81</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>82</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>84</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>87</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>88</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>89</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>93</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>96</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>97</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>98</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>99</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>100</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>102</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>103</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>105</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>106</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>107</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>108</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>109</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>111</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>112</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>113</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>114</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>116</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>117</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>118</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>119</v>
       </c>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DCB26F-CA0E-4B5A-846E-CBDF9B846734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395CBCB7-7869-445A-AD54-25B549B14A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -160,9 +160,6 @@
     <t>term_head_sub_exe</t>
   </si>
   <si>
-    <t>change_head_sub_exe</t>
-  </si>
-  <si>
     <t>cumulative_changes_head_sub_exe</t>
   </si>
   <si>
@@ -178,24 +175,12 @@
     <t>Subnational Executive Elections Dataset (SEED)</t>
   </si>
   <si>
-    <t>reelec_sub_exe</t>
-  </si>
-  <si>
-    <t>years_contin_sub_exe</t>
-  </si>
-  <si>
     <t>head_party_sub_exe</t>
   </si>
   <si>
-    <t>change_party_sub_exe</t>
-  </si>
-  <si>
     <t>cumulative_changes_party_sub_exe</t>
   </si>
   <si>
-    <t>years_party_contin_sub_exe</t>
-  </si>
-  <si>
     <t>ideo_party_sub_exe</t>
   </si>
   <si>
@@ -677,6 +662,21 @@
   </si>
   <si>
     <t>#C5CA8A,#5E304F,#5FBFF9</t>
+  </si>
+  <si>
+    <t>consecutive_reelection_sub_exe</t>
+  </si>
+  <si>
+    <t>cumulative_years_in_power_sub_exe</t>
+  </si>
+  <si>
+    <t>cumulative_years_in_power_party_sub_exe</t>
+  </si>
+  <si>
+    <t>turnover_head_sub_exe</t>
+  </si>
+  <si>
+    <t>turnover_party_sub_exe</t>
   </si>
 </sst>
 </file>
@@ -1025,20 +1025,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="84.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="84.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1070,7 +1070,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1096,7 +1096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1148,7 +1148,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1174,15 +1174,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -1203,15 +1203,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -1235,15 +1235,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -1264,15 +1264,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -1296,15 +1296,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -1328,15 +1328,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -1360,15 +1360,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -1389,15 +1389,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -1421,15 +1421,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -1453,15 +1453,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -1482,15 +1482,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -1502,7 +1502,7 @@
         <v>28</v>
       </c>
       <c r="G16" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1514,15 +1514,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -1543,15 +1543,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -1575,15 +1575,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -1607,15 +1607,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
@@ -1639,21 +1639,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" t="s">
         <v>49</v>
-      </c>
-      <c r="E21" t="s">
-        <v>50</v>
       </c>
       <c r="F21" t="s">
         <v>35</v>
@@ -1671,21 +1671,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" t="s">
         <v>49</v>
-      </c>
-      <c r="E22" t="s">
-        <v>50</v>
       </c>
       <c r="F22" t="s">
         <v>35</v>
@@ -1703,15 +1703,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
@@ -1735,15 +1735,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -1764,15 +1764,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>217</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
@@ -1796,15 +1796,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
@@ -1828,15 +1828,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
@@ -1860,15 +1860,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -1892,21 +1892,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" t="s">
         <v>49</v>
-      </c>
-      <c r="E29" t="s">
-        <v>50</v>
       </c>
       <c r="F29" t="s">
         <v>35</v>
@@ -1924,21 +1924,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>16</v>
@@ -1956,15 +1956,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
@@ -1988,15 +1988,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
@@ -2020,21 +2020,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" t="s">
         <v>49</v>
-      </c>
-      <c r="E33" t="s">
-        <v>50</v>
       </c>
       <c r="F33" t="s">
         <v>35</v>
@@ -2052,21 +2052,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" t="s">
         <v>49</v>
-      </c>
-      <c r="E34" t="s">
-        <v>50</v>
       </c>
       <c r="F34" t="s">
         <v>31</v>
@@ -2081,27 +2081,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" t="s">
         <v>49</v>
-      </c>
-      <c r="E35" t="s">
-        <v>50</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -2113,91 +2113,91 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" t="s">
         <v>49</v>
-      </c>
-      <c r="E36" t="s">
-        <v>50</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
       </c>
       <c r="G36" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>65</v>
       </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="J36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" t="s">
-        <v>206</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="B38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" t="s">
         <v>49</v>
-      </c>
-      <c r="E37" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" t="s">
-        <v>68</v>
-      </c>
-      <c r="G37" t="s">
-        <v>69</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" t="s">
-        <v>153</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" t="s">
-        <v>50</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -2209,27 +2209,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" t="s">
         <v>49</v>
       </c>
-      <c r="E39" t="s">
-        <v>50</v>
-      </c>
       <c r="F39" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G39" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2241,27 +2241,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" t="s">
         <v>49</v>
-      </c>
-      <c r="E40" t="s">
-        <v>50</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2273,59 +2273,59 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="F41" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>69</v>
       </c>
-      <c r="H41" s="1">
-        <v>1</v>
-      </c>
-      <c r="I41" s="1">
-        <v>1</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>74</v>
-      </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" t="s">
         <v>49</v>
-      </c>
-      <c r="E42" t="s">
-        <v>50</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -2337,27 +2337,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43" t="s">
         <v>49</v>
       </c>
-      <c r="E43" t="s">
-        <v>50</v>
-      </c>
       <c r="F43" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G43" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -2369,27 +2369,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" t="s">
         <v>49</v>
-      </c>
-      <c r="E44" t="s">
-        <v>50</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -2401,27 +2401,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D45" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" t="s">
         <v>49</v>
       </c>
-      <c r="E45" t="s">
-        <v>50</v>
-      </c>
       <c r="F45" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G45" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2433,27 +2433,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46" t="s">
         <v>49</v>
-      </c>
-      <c r="E46" t="s">
-        <v>50</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -2465,27 +2465,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B47" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D47" t="s">
+        <v>48</v>
+      </c>
+      <c r="E47" t="s">
         <v>49</v>
       </c>
-      <c r="E47" t="s">
-        <v>50</v>
-      </c>
       <c r="F47" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G47" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -2497,27 +2497,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" t="s">
         <v>49</v>
       </c>
-      <c r="E48" t="s">
-        <v>50</v>
-      </c>
       <c r="F48" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G48" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -2529,27 +2529,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D49" t="s">
+        <v>48</v>
+      </c>
+      <c r="E49" t="s">
         <v>49</v>
-      </c>
-      <c r="E49" t="s">
-        <v>50</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2561,541 +2561,541 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E50" t="s">
+        <v>49</v>
+      </c>
+      <c r="F50" t="s">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>82</v>
       </c>
-      <c r="B50" t="s">
-        <v>160</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D50" t="s">
-        <v>49</v>
-      </c>
-      <c r="E50" t="s">
-        <v>50</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="D52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>83</v>
       </c>
-      <c r="G50" t="s">
-        <v>65</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-      <c r="J50" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="D53" t="s">
+        <v>48</v>
+      </c>
+      <c r="E53" t="s">
+        <v>81</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>84</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D54" t="s">
+        <v>48</v>
+      </c>
+      <c r="E54" t="s">
+        <v>81</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>85</v>
       </c>
-      <c r="E51" t="s">
+      <c r="D55" t="s">
+        <v>48</v>
+      </c>
+      <c r="E55" t="s">
+        <v>81</v>
+      </c>
+      <c r="G55" t="s">
+        <v>64</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="D56" t="s">
+        <v>48</v>
+      </c>
+      <c r="E56" t="s">
+        <v>81</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>87</v>
       </c>
-      <c r="D52" t="s">
-        <v>49</v>
-      </c>
-      <c r="E52" t="s">
-        <v>86</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="D57" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" t="s">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s">
+        <v>64</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>88</v>
       </c>
-      <c r="D53" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" t="s">
-        <v>86</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="D58" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>89</v>
       </c>
-      <c r="D54" t="s">
-        <v>49</v>
-      </c>
-      <c r="E54" t="s">
-        <v>86</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="D59" t="s">
+        <v>48</v>
+      </c>
+      <c r="E59" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>90</v>
       </c>
-      <c r="D55" t="s">
-        <v>49</v>
-      </c>
-      <c r="E55" t="s">
-        <v>86</v>
-      </c>
-      <c r="G55" t="s">
-        <v>69</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="D60" t="s">
+        <v>48</v>
+      </c>
+      <c r="E60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>91</v>
       </c>
-      <c r="D56" t="s">
-        <v>49</v>
-      </c>
-      <c r="E56" t="s">
-        <v>86</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="D61" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>92</v>
       </c>
-      <c r="D57" t="s">
-        <v>49</v>
-      </c>
-      <c r="E57" t="s">
-        <v>86</v>
-      </c>
-      <c r="G57" t="s">
-        <v>69</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="D62" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>93</v>
       </c>
-      <c r="D58" t="s">
-        <v>49</v>
-      </c>
-      <c r="E58" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="D63" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>94</v>
       </c>
-      <c r="D59" t="s">
-        <v>49</v>
-      </c>
-      <c r="E59" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="D64" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>95</v>
       </c>
-      <c r="D60" t="s">
-        <v>49</v>
-      </c>
-      <c r="E60" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="D65" t="s">
+        <v>48</v>
+      </c>
+      <c r="E65" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>96</v>
       </c>
-      <c r="D61" t="s">
-        <v>49</v>
-      </c>
-      <c r="E61" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="D66" t="s">
+        <v>48</v>
+      </c>
+      <c r="E66" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>97</v>
       </c>
-      <c r="D62" t="s">
-        <v>49</v>
-      </c>
-      <c r="E62" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="D67" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>98</v>
       </c>
-      <c r="D63" t="s">
-        <v>49</v>
-      </c>
-      <c r="E63" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="D68" t="s">
+        <v>48</v>
+      </c>
+      <c r="E68" t="s">
+        <v>81</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>100</v>
+      </c>
+      <c r="D69" t="s">
+        <v>48</v>
+      </c>
+      <c r="E69" t="s">
+        <v>81</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>101</v>
+      </c>
+      <c r="D70" t="s">
+        <v>48</v>
+      </c>
+      <c r="E70" t="s">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s">
         <v>99</v>
       </c>
-      <c r="D64" t="s">
-        <v>49</v>
-      </c>
-      <c r="E64" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>100</v>
-      </c>
-      <c r="D65" t="s">
-        <v>49</v>
-      </c>
-      <c r="E65" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>101</v>
-      </c>
-      <c r="D66" t="s">
-        <v>49</v>
-      </c>
-      <c r="E66" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>102</v>
       </c>
-      <c r="D67" t="s">
-        <v>49</v>
-      </c>
-      <c r="E67" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="D71" t="s">
+        <v>48</v>
+      </c>
+      <c r="E71" t="s">
+        <v>81</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>103</v>
       </c>
-      <c r="D68" t="s">
-        <v>49</v>
-      </c>
-      <c r="E68" t="s">
-        <v>86</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="D72" t="s">
+        <v>48</v>
+      </c>
+      <c r="E72" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>104</v>
+      </c>
+      <c r="D73" t="s">
+        <v>48</v>
+      </c>
+      <c r="E73" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>105</v>
       </c>
-      <c r="D69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E69" t="s">
-        <v>86</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="D74" t="s">
+        <v>48</v>
+      </c>
+      <c r="E74" t="s">
+        <v>81</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>106</v>
       </c>
-      <c r="D70" t="s">
-        <v>49</v>
-      </c>
-      <c r="E70" t="s">
-        <v>86</v>
-      </c>
-      <c r="G70" t="s">
-        <v>104</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="D75" t="s">
+        <v>48</v>
+      </c>
+      <c r="E75" t="s">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s">
+        <v>64</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>107</v>
       </c>
-      <c r="D71" t="s">
-        <v>49</v>
-      </c>
-      <c r="E71" t="s">
-        <v>86</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="D76" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76" t="s">
+        <v>81</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>108</v>
       </c>
-      <c r="D72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E72" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="D77" t="s">
+        <v>48</v>
+      </c>
+      <c r="E77" t="s">
+        <v>81</v>
+      </c>
+      <c r="G77" t="s">
+        <v>64</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>109</v>
       </c>
-      <c r="D73" t="s">
-        <v>49</v>
-      </c>
-      <c r="E73" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="D78" t="s">
+        <v>48</v>
+      </c>
+      <c r="E78" t="s">
+        <v>81</v>
+      </c>
+      <c r="G78" t="s">
         <v>110</v>
       </c>
-      <c r="D74" t="s">
-        <v>49</v>
-      </c>
-      <c r="E74" t="s">
-        <v>86</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>111</v>
       </c>
-      <c r="D75" t="s">
-        <v>49</v>
-      </c>
-      <c r="E75" t="s">
-        <v>86</v>
-      </c>
-      <c r="G75" t="s">
-        <v>69</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="D79" t="s">
+        <v>48</v>
+      </c>
+      <c r="E79" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>112</v>
       </c>
-      <c r="D76" t="s">
-        <v>49</v>
-      </c>
-      <c r="E76" t="s">
-        <v>86</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="D80" t="s">
+        <v>48</v>
+      </c>
+      <c r="E80" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>113</v>
       </c>
-      <c r="D77" t="s">
-        <v>49</v>
-      </c>
-      <c r="E77" t="s">
-        <v>86</v>
-      </c>
-      <c r="G77" t="s">
-        <v>69</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="D81" t="s">
+        <v>48</v>
+      </c>
+      <c r="E81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>114</v>
       </c>
-      <c r="D78" t="s">
-        <v>49</v>
-      </c>
-      <c r="E78" t="s">
-        <v>86</v>
-      </c>
-      <c r="G78" t="s">
-        <v>115</v>
-      </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>116</v>
-      </c>
-      <c r="D79" t="s">
-        <v>49</v>
-      </c>
-      <c r="E79" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>117</v>
-      </c>
-      <c r="D80" t="s">
-        <v>49</v>
-      </c>
-      <c r="E80" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>118</v>
-      </c>
-      <c r="D81" t="s">
-        <v>49</v>
-      </c>
-      <c r="E81" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>119</v>
-      </c>
       <c r="D82" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E82" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H82">
         <v>0</v>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395CBCB7-7869-445A-AD54-25B549B14A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83A9858-A86E-43A0-B2A0-20E4C18C31BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="285">
   <si>
     <t>variable</t>
   </si>
@@ -100,9 +100,6 @@
     <t>Executive</t>
   </si>
   <si>
-    <t>National Executive Dataset (NED)</t>
-  </si>
-  <si>
     <t>text</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>#d73027,#fc8d59,#91bfdb,#4575b4</t>
   </si>
   <si>
-    <t>Subnational Executive Dataset (SED)</t>
-  </si>
-  <si>
     <t>sex_head_sub_exe</t>
   </si>
   <si>
@@ -172,9 +166,6 @@
     <t>Electoral</t>
   </si>
   <si>
-    <t>Subnational Executive Elections Dataset (SEED)</t>
-  </si>
-  <si>
     <t>head_party_sub_exe</t>
   </si>
   <si>
@@ -268,12 +259,6 @@
     <t>Electoral Subnational Legislative</t>
   </si>
   <si>
-    <t>Subnational Legislative Elections Dataset (SLED)</t>
-  </si>
-  <si>
-    <t>date_electoral_sub_leg</t>
-  </si>
-  <si>
     <t>voters_registered_sub_leg</t>
   </si>
   <si>
@@ -292,18 +277,6 @@
     <t>party_name_sub_leg</t>
   </si>
   <si>
-    <t>total_votes_party</t>
-  </si>
-  <si>
-    <t>ratio_votes_party</t>
-  </si>
-  <si>
-    <t>total_seats_party</t>
-  </si>
-  <si>
-    <t>ratio_seats_party</t>
-  </si>
-  <si>
     <t>blank_votes_sub_leg</t>
   </si>
   <si>
@@ -313,9 +286,6 @@
     <t>challenged_votes_sub_leg</t>
   </si>
   <si>
-    <t>impounded_votes_sub_leg</t>
-  </si>
-  <si>
     <t>compensation_for_record_discrepancy_votes_sub_leg</t>
   </si>
   <si>
@@ -367,9 +337,6 @@
     <t>electoral_system_sub_leg</t>
   </si>
   <si>
-    <t>enp_leg_sub_leg</t>
-  </si>
-  <si>
     <t>dataset</t>
   </si>
   <si>
@@ -677,6 +644,240 @@
   </si>
   <si>
     <t>turnover_party_sub_exe</t>
+  </si>
+  <si>
+    <t>NED</t>
+  </si>
+  <si>
+    <t>SED</t>
+  </si>
+  <si>
+    <t>SEED</t>
+  </si>
+  <si>
+    <t>SLED</t>
+  </si>
+  <si>
+    <t>Chamber Election</t>
+  </si>
+  <si>
+    <t>Indicates chamber where elections held</t>
+  </si>
+  <si>
+    <t>Registered Voters Leg.</t>
+  </si>
+  <si>
+    <t>Total registered voters in legislative elections</t>
+  </si>
+  <si>
+    <t>Total Voters Leg.</t>
+  </si>
+  <si>
+    <t>Total voters in legislative elections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voter Turnout Leg. (%) </t>
+  </si>
+  <si>
+    <t>Voter turnout rate</t>
+  </si>
+  <si>
+    <t>Total valid votes</t>
+  </si>
+  <si>
+    <t>Valid votes as % of total</t>
+  </si>
+  <si>
+    <t>Party or coalition name</t>
+  </si>
+  <si>
+    <t>Number of blank votes</t>
+  </si>
+  <si>
+    <t>Number of null votes</t>
+  </si>
+  <si>
+    <t>Number of challenged votes</t>
+  </si>
+  <si>
+    <t>Votes adjusted due to tally sheet discrepancy</t>
+  </si>
+  <si>
+    <t>Margin between winner and runner-up</t>
+  </si>
+  <si>
+    <t>Cumulative count of legislative elections</t>
+  </si>
+  <si>
+    <t>Whether legislative and presidential elections held same year</t>
+  </si>
+  <si>
+    <t>Number of Parties Leg.</t>
+  </si>
+  <si>
+    <t>Parties competing in election</t>
+  </si>
+  <si>
+    <t>Seats in Contest Leg.</t>
+  </si>
+  <si>
+    <t>Total seats contested</t>
+  </si>
+  <si>
+    <t>Total Chamber Seats Leg.</t>
+  </si>
+  <si>
+    <t>Total seats in legislature</t>
+  </si>
+  <si>
+    <t>Incumbent Seats Leg.</t>
+  </si>
+  <si>
+    <t>Seats held by governor's party</t>
+  </si>
+  <si>
+    <t>Incumbent Seats Leg. (%)</t>
+  </si>
+  <si>
+    <t>Governor's party seats share</t>
+  </si>
+  <si>
+    <t>Opposition Seats Leg.</t>
+  </si>
+  <si>
+    <t>Seats held by opposition parties</t>
+  </si>
+  <si>
+    <t>Opposition Seats Leg. (%)</t>
+  </si>
+  <si>
+    <t>Opposition seat share</t>
+  </si>
+  <si>
+    <t>Chamber Structure Leg.</t>
+  </si>
+  <si>
+    <t>Number of legislative chambers</t>
+  </si>
+  <si>
+    <t>Term Length Leg.</t>
+  </si>
+  <si>
+    <t>Length of legislative term in years</t>
+  </si>
+  <si>
+    <t>Renewal Type Leg.</t>
+  </si>
+  <si>
+    <t>Type of chamber renewal</t>
+  </si>
+  <si>
+    <t>Electoral System Leg.</t>
+  </si>
+  <si>
+    <t>Electoral system of chamber</t>
+  </si>
+  <si>
+    <t>total_seats_party_sub_leg</t>
+  </si>
+  <si>
+    <t>Party Seats</t>
+  </si>
+  <si>
+    <t>Seats won by a party</t>
+  </si>
+  <si>
+    <t>Legislative</t>
+  </si>
+  <si>
+    <t>numeric</t>
+  </si>
+  <si>
+    <t>total_votes_party_sub_leg</t>
+  </si>
+  <si>
+    <t>Total votes for a party/coalition</t>
+  </si>
+  <si>
+    <t>enp_sub_leg</t>
+  </si>
+  <si>
+    <t>Effective Number of Parties Leg.</t>
+  </si>
+  <si>
+    <t>Index of party system fragmentation</t>
+  </si>
+  <si>
+    <t>contested_votes_sub_leg</t>
+  </si>
+  <si>
+    <t>Votes with contested identity</t>
+  </si>
+  <si>
+    <t>date_election_sub_leg</t>
+  </si>
+  <si>
+    <t>Date of subnational legislative elections</t>
+  </si>
+  <si>
+    <t>perc_votes_party_sub_leg</t>
+  </si>
+  <si>
+    <t>Party vote share</t>
+  </si>
+  <si>
+    <t>perc_seats_party_sub_leg</t>
+  </si>
+  <si>
+    <t>Party Seats (%)</t>
+  </si>
+  <si>
+    <t>Seats as % of total contested</t>
+  </si>
+  <si>
+    <t>Valid Votes Leg.</t>
+  </si>
+  <si>
+    <t>Valid Votes Leg. (%)</t>
+  </si>
+  <si>
+    <t>Party Name Leg.</t>
+  </si>
+  <si>
+    <t>Blank Votes Leg.</t>
+  </si>
+  <si>
+    <t>Null Votes Leg.</t>
+  </si>
+  <si>
+    <t>Challenged Votes Leg.</t>
+  </si>
+  <si>
+    <t>Record Discrepancy Votes Leg.</t>
+  </si>
+  <si>
+    <t>Margin of Victory Leg. (%)</t>
+  </si>
+  <si>
+    <t>Cumulative Elections Leg.</t>
+  </si>
+  <si>
+    <t>Concurrent with National Election Leg.</t>
+  </si>
+  <si>
+    <t>Party Votes Leg.</t>
+  </si>
+  <si>
+    <t>Contested Votes Leg.</t>
+  </si>
+  <si>
+    <t>Election Date Leg.</t>
+  </si>
+  <si>
+    <t>Party Votes Leg. (%)</t>
+  </si>
+  <si>
+    <t>per_chamber</t>
   </si>
 </sst>
 </file>
@@ -1024,13 +1225,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J82"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="84.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="43.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31.85546875" bestFit="1" customWidth="1"/>
@@ -1038,7 +1240,7 @@
     <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1254,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1069,8 +1271,11 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1078,7 +1283,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1096,7 +1301,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1104,7 +1309,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1122,7 +1327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1130,7 +1335,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1148,7 +1353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1156,7 +1361,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1174,24 +1379,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
       </c>
       <c r="E6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" t="s">
         <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1203,27 +1408,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
         <v>28</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1235,24 +1440,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1264,27 +1469,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1296,27 +1501,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" t="s">
         <v>35</v>
-      </c>
-      <c r="G10" t="s">
-        <v>36</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1328,27 +1533,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
         <v>35</v>
-      </c>
-      <c r="G11" t="s">
-        <v>36</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1360,21 +1565,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -1389,27 +1594,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" t="s">
         <v>40</v>
-      </c>
-      <c r="G13" t="s">
-        <v>41</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1421,27 +1626,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="F14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
         <v>35</v>
-      </c>
-      <c r="G14" t="s">
-        <v>36</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1453,24 +1658,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1482,56 +1687,56 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
       </c>
       <c r="E16" t="s">
+        <v>208</v>
+      </c>
+      <c r="F16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" t="s">
+        <v>201</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>42</v>
       </c>
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" t="s">
-        <v>212</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1543,28 +1748,28 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" t="s">
         <v>35</v>
       </c>
-      <c r="G18" t="s">
-        <v>36</v>
-      </c>
       <c r="H18">
         <v>0</v>
       </c>
@@ -1575,27 +1780,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1607,27 +1812,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1641,25 +1846,25 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" t="s">
         <v>35</v>
-      </c>
-      <c r="G21" t="s">
-        <v>36</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1673,26 +1878,26 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F22" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" t="s">
         <v>35</v>
       </c>
-      <c r="G22" t="s">
-        <v>36</v>
-      </c>
       <c r="H22">
         <v>1</v>
       </c>
@@ -1703,27 +1908,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B23" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1735,21 +1940,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -1764,28 +1969,28 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" t="s">
         <v>35</v>
       </c>
-      <c r="G25" t="s">
-        <v>36</v>
-      </c>
       <c r="H25">
         <v>0</v>
       </c>
@@ -1796,27 +2001,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1828,27 +2033,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1860,28 +2065,28 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F28" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" t="s">
         <v>40</v>
       </c>
-      <c r="G28" t="s">
-        <v>41</v>
-      </c>
       <c r="H28">
         <v>1</v>
       </c>
@@ -1892,27 +2097,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F29" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" t="s">
         <v>35</v>
-      </c>
-      <c r="G29" t="s">
-        <v>36</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -1926,25 +2131,25 @@
     </row>
     <row r="30" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="E30" t="s">
+        <v>209</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
@@ -1956,28 +2161,28 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" t="s">
         <v>35</v>
       </c>
-      <c r="G31" t="s">
-        <v>36</v>
-      </c>
       <c r="H31">
         <v>1</v>
       </c>
@@ -1988,27 +2193,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="F32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" t="s">
         <v>35</v>
-      </c>
-      <c r="G32" t="s">
-        <v>36</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -2022,26 +2227,26 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F33" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" t="s">
         <v>35</v>
       </c>
-      <c r="G33" t="s">
-        <v>36</v>
-      </c>
       <c r="H33">
         <v>1</v>
       </c>
@@ -2052,24 +2257,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2083,25 +2288,25 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -2115,25 +2320,25 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2147,25 +2352,25 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G37" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2179,25 +2384,25 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -2211,25 +2416,25 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2243,25 +2448,25 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2275,25 +2480,25 @@
     </row>
     <row r="41" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="E41" t="s">
+        <v>209</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H41" s="1">
         <v>1</v>
@@ -2307,25 +2512,25 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -2339,25 +2544,25 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F43" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G43" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -2371,25 +2576,25 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D44" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -2403,25 +2608,25 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F45" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G45" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2435,25 +2640,25 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D46" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -2467,25 +2672,25 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" t="s">
         <v>209</v>
       </c>
-      <c r="D47" t="s">
-        <v>48</v>
-      </c>
-      <c r="E47" t="s">
-        <v>49</v>
-      </c>
       <c r="F47" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -2499,25 +2704,25 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F48" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G48" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -2529,457 +2734,928 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E49" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
       </c>
       <c r="G49" t="s">
+        <v>57</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" t="s">
+        <v>46</v>
+      </c>
+      <c r="E50" t="s">
+        <v>209</v>
+      </c>
+      <c r="F50" t="s">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" t="s">
+        <v>211</v>
+      </c>
+      <c r="C51" t="s">
+        <v>212</v>
+      </c>
+      <c r="D51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" t="s">
+        <v>210</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52" t="s">
+        <v>213</v>
+      </c>
+      <c r="C52" t="s">
+        <v>214</v>
+      </c>
+      <c r="D52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" t="s">
+        <v>210</v>
+      </c>
+      <c r="F52" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" t="s">
+        <v>57</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" t="s">
+        <v>215</v>
+      </c>
+      <c r="C53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" t="s">
+        <v>210</v>
+      </c>
+      <c r="F53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" t="s">
+        <v>57</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" t="s">
+        <v>217</v>
+      </c>
+      <c r="C54" t="s">
+        <v>218</v>
+      </c>
+      <c r="D54" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" t="s">
+        <v>210</v>
+      </c>
+      <c r="F54" t="s">
         <v>60</v>
       </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
-      </c>
-      <c r="J49" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>77</v>
-      </c>
-      <c r="B50" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D50" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" t="s">
-        <v>49</v>
-      </c>
-      <c r="F50" t="s">
-        <v>78</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="G54" t="s">
+        <v>61</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>81</v>
+      </c>
+      <c r="B55" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" t="s">
+        <v>219</v>
+      </c>
+      <c r="D55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55" t="s">
+        <v>210</v>
+      </c>
+      <c r="F55" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" t="s">
+        <v>57</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" t="s">
+        <v>220</v>
+      </c>
+      <c r="D56" t="s">
+        <v>46</v>
+      </c>
+      <c r="E56" t="s">
+        <v>210</v>
+      </c>
+      <c r="F56" t="s">
         <v>60</v>
       </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-      <c r="J50" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" t="s">
-        <v>80</v>
-      </c>
-      <c r="E51" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>82</v>
-      </c>
-      <c r="D52" t="s">
-        <v>48</v>
-      </c>
-      <c r="E52" t="s">
-        <v>81</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="G56" t="s">
+        <v>61</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>83</v>
       </c>
-      <c r="D53" t="s">
-        <v>48</v>
-      </c>
-      <c r="E53" t="s">
-        <v>81</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B57" t="s">
+        <v>272</v>
+      </c>
+      <c r="C57" t="s">
+        <v>221</v>
+      </c>
+      <c r="D57" t="s">
+        <v>46</v>
+      </c>
+      <c r="E57" t="s">
+        <v>210</v>
+      </c>
+      <c r="F57" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>84</v>
       </c>
-      <c r="D54" t="s">
-        <v>48</v>
-      </c>
-      <c r="E54" t="s">
-        <v>81</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B58" t="s">
+        <v>273</v>
+      </c>
+      <c r="C58" t="s">
+        <v>222</v>
+      </c>
+      <c r="D58" t="s">
+        <v>46</v>
+      </c>
+      <c r="E58" t="s">
+        <v>210</v>
+      </c>
+      <c r="F58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>85</v>
       </c>
-      <c r="D55" t="s">
-        <v>48</v>
-      </c>
-      <c r="E55" t="s">
-        <v>81</v>
-      </c>
-      <c r="G55" t="s">
-        <v>64</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="B59" t="s">
+        <v>274</v>
+      </c>
+      <c r="C59" t="s">
+        <v>223</v>
+      </c>
+      <c r="D59" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" t="s">
+        <v>210</v>
+      </c>
+      <c r="F59" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" t="s">
+        <v>57</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>86</v>
       </c>
-      <c r="D56" t="s">
-        <v>48</v>
-      </c>
-      <c r="E56" t="s">
-        <v>81</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" t="s">
+        <v>224</v>
+      </c>
+      <c r="D60" t="s">
+        <v>46</v>
+      </c>
+      <c r="E60" t="s">
+        <v>210</v>
+      </c>
+      <c r="F60" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" t="s">
+        <v>57</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60" t="s">
+        <v>20</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>87</v>
       </c>
-      <c r="D57" t="s">
-        <v>48</v>
-      </c>
-      <c r="E57" t="s">
-        <v>81</v>
-      </c>
-      <c r="G57" t="s">
-        <v>64</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="B61" t="s">
+        <v>276</v>
+      </c>
+      <c r="C61" t="s">
+        <v>225</v>
+      </c>
+      <c r="D61" t="s">
+        <v>46</v>
+      </c>
+      <c r="E61" t="s">
+        <v>210</v>
+      </c>
+      <c r="F61" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" t="s">
+        <v>57</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>88</v>
       </c>
-      <c r="D58" t="s">
-        <v>48</v>
-      </c>
-      <c r="E58" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="B62" t="s">
+        <v>277</v>
+      </c>
+      <c r="C62" t="s">
+        <v>226</v>
+      </c>
+      <c r="D62" t="s">
+        <v>46</v>
+      </c>
+      <c r="E62" t="s">
+        <v>210</v>
+      </c>
+      <c r="F62" t="s">
+        <v>60</v>
+      </c>
+      <c r="G62" t="s">
+        <v>61</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63" t="s">
+        <v>278</v>
+      </c>
+      <c r="C63" t="s">
+        <v>227</v>
+      </c>
+      <c r="D63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E63" t="s">
+        <v>210</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" t="s">
+        <v>279</v>
+      </c>
+      <c r="C64" t="s">
+        <v>228</v>
+      </c>
+      <c r="D64" t="s">
+        <v>46</v>
+      </c>
+      <c r="E64" t="s">
+        <v>210</v>
+      </c>
+      <c r="F64" t="s">
+        <v>34</v>
+      </c>
+      <c r="G64" t="s">
         <v>89</v>
       </c>
-      <c r="D59" t="s">
-        <v>48</v>
-      </c>
-      <c r="E59" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>91</v>
-      </c>
-      <c r="D61" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>92</v>
       </c>
-      <c r="D62" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="B65" t="s">
+        <v>229</v>
+      </c>
+      <c r="C65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E65" t="s">
+        <v>210</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>93</v>
       </c>
-      <c r="D63" t="s">
-        <v>48</v>
-      </c>
-      <c r="E63" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="B66" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" t="s">
+        <v>232</v>
+      </c>
+      <c r="D66" t="s">
+        <v>46</v>
+      </c>
+      <c r="E66" t="s">
+        <v>210</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>94</v>
       </c>
-      <c r="D64" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B67" t="s">
+        <v>233</v>
+      </c>
+      <c r="C67" t="s">
+        <v>234</v>
+      </c>
+      <c r="D67" t="s">
+        <v>46</v>
+      </c>
+      <c r="E67" t="s">
+        <v>210</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>95</v>
       </c>
-      <c r="D65" t="s">
-        <v>48</v>
-      </c>
-      <c r="E65" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B68" t="s">
+        <v>235</v>
+      </c>
+      <c r="C68" t="s">
+        <v>236</v>
+      </c>
+      <c r="D68" t="s">
+        <v>46</v>
+      </c>
+      <c r="E68" t="s">
+        <v>210</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>96</v>
       </c>
-      <c r="D66" t="s">
-        <v>48</v>
-      </c>
-      <c r="E66" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B69" t="s">
+        <v>237</v>
+      </c>
+      <c r="C69" t="s">
+        <v>238</v>
+      </c>
+      <c r="D69" t="s">
+        <v>46</v>
+      </c>
+      <c r="E69" t="s">
+        <v>210</v>
+      </c>
+      <c r="F69" t="s">
+        <v>60</v>
+      </c>
+      <c r="G69" t="s">
+        <v>61</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>97</v>
       </c>
-      <c r="D67" t="s">
-        <v>48</v>
-      </c>
-      <c r="E67" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="B70" t="s">
+        <v>239</v>
+      </c>
+      <c r="C70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D70" t="s">
+        <v>46</v>
+      </c>
+      <c r="E70" t="s">
+        <v>210</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>98</v>
       </c>
-      <c r="D68" t="s">
-        <v>48</v>
-      </c>
-      <c r="E68" t="s">
-        <v>81</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B71" t="s">
+        <v>241</v>
+      </c>
+      <c r="C71" t="s">
+        <v>242</v>
+      </c>
+      <c r="D71" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71" t="s">
+        <v>210</v>
+      </c>
+      <c r="F71" t="s">
+        <v>60</v>
+      </c>
+      <c r="G71" t="s">
+        <v>61</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
+        <v>20</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" t="s">
+        <v>243</v>
+      </c>
+      <c r="C72" t="s">
+        <v>244</v>
+      </c>
+      <c r="D72" t="s">
+        <v>46</v>
+      </c>
+      <c r="E72" t="s">
+        <v>210</v>
+      </c>
+      <c r="F72" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" t="s">
         <v>100</v>
       </c>
-      <c r="D69" t="s">
-        <v>48</v>
-      </c>
-      <c r="E69" t="s">
-        <v>81</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72" t="s">
+        <v>20</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>101</v>
       </c>
-      <c r="D70" t="s">
-        <v>48</v>
-      </c>
-      <c r="E70" t="s">
-        <v>81</v>
-      </c>
-      <c r="G70" t="s">
-        <v>99</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B73" t="s">
+        <v>245</v>
+      </c>
+      <c r="C73" t="s">
+        <v>246</v>
+      </c>
+      <c r="D73" t="s">
+        <v>46</v>
+      </c>
+      <c r="E73" t="s">
+        <v>210</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>102</v>
       </c>
-      <c r="D71" t="s">
-        <v>48</v>
-      </c>
-      <c r="E71" t="s">
-        <v>81</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B74" t="s">
+        <v>247</v>
+      </c>
+      <c r="C74" t="s">
+        <v>248</v>
+      </c>
+      <c r="D74" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74" t="s">
+        <v>210</v>
+      </c>
+      <c r="F74" t="s">
+        <v>12</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
+        <v>20</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>103</v>
       </c>
-      <c r="D72" t="s">
-        <v>48</v>
-      </c>
-      <c r="E72" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>104</v>
-      </c>
-      <c r="D73" t="s">
-        <v>48</v>
-      </c>
-      <c r="E73" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>105</v>
-      </c>
-      <c r="D74" t="s">
-        <v>48</v>
-      </c>
-      <c r="E74" t="s">
-        <v>81</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>106</v>
+      <c r="B75" t="s">
+        <v>249</v>
+      </c>
+      <c r="C75" t="s">
+        <v>250</v>
       </c>
       <c r="D75" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E75" t="s">
-        <v>81</v>
-      </c>
-      <c r="G75" t="s">
-        <v>64</v>
+        <v>210</v>
+      </c>
+      <c r="F75" t="s">
+        <v>12</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -2987,16 +3663,28 @@
       <c r="J75" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>251</v>
+      </c>
+      <c r="B76" t="s">
+        <v>252</v>
+      </c>
+      <c r="C76" t="s">
+        <v>253</v>
       </c>
       <c r="D76" t="s">
-        <v>48</v>
+        <v>254</v>
       </c>
       <c r="E76" t="s">
-        <v>81</v>
+        <v>210</v>
+      </c>
+      <c r="F76" t="s">
+        <v>255</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -3007,19 +3695,28 @@
       <c r="J76" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>256</v>
+      </c>
+      <c r="B77" t="s">
+        <v>280</v>
+      </c>
+      <c r="C77" t="s">
+        <v>257</v>
       </c>
       <c r="D77" t="s">
-        <v>48</v>
+        <v>254</v>
       </c>
       <c r="E77" t="s">
-        <v>81</v>
-      </c>
-      <c r="G77" t="s">
-        <v>64</v>
+        <v>210</v>
+      </c>
+      <c r="F77" t="s">
+        <v>255</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3030,72 +3727,159 @@
       <c r="J77" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>109</v>
+        <v>258</v>
+      </c>
+      <c r="B78" t="s">
+        <v>259</v>
+      </c>
+      <c r="C78" t="s">
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>48</v>
+        <v>254</v>
       </c>
       <c r="E78" t="s">
-        <v>81</v>
+        <v>210</v>
+      </c>
+      <c r="F78" t="s">
+        <v>75</v>
       </c>
       <c r="G78" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>111</v>
+        <v>261</v>
+      </c>
+      <c r="B79" t="s">
+        <v>281</v>
+      </c>
+      <c r="C79" t="s">
+        <v>262</v>
       </c>
       <c r="D79" t="s">
-        <v>48</v>
+        <v>254</v>
       </c>
       <c r="E79" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="F79" t="s">
+        <v>255</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79" t="s">
+        <v>20</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>112</v>
+        <v>263</v>
+      </c>
+      <c r="B80" t="s">
+        <v>282</v>
+      </c>
+      <c r="C80" t="s">
+        <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>48</v>
+        <v>254</v>
       </c>
       <c r="E80" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="F80" t="s">
+        <v>30</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>113</v>
+        <v>265</v>
+      </c>
+      <c r="B81" t="s">
+        <v>283</v>
+      </c>
+      <c r="C81" t="s">
+        <v>266</v>
       </c>
       <c r="D81" t="s">
-        <v>48</v>
+        <v>254</v>
       </c>
       <c r="E81" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="F81" t="s">
+        <v>255</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81" t="s">
+        <v>20</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>114</v>
+        <v>267</v>
+      </c>
+      <c r="B82" t="s">
+        <v>268</v>
+      </c>
+      <c r="C82" t="s">
+        <v>269</v>
       </c>
       <c r="D82" t="s">
-        <v>48</v>
+        <v>254</v>
       </c>
       <c r="E82" t="s">
-        <v>81</v>
+        <v>210</v>
+      </c>
+      <c r="F82" t="s">
+        <v>255</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3106,9 +3890,24 @@
       <c r="J82" t="s">
         <v>20</v>
       </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J82" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J82" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="SEED"/>
+        <filter val="SLED"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83A9858-A86E-43A0-B2A0-20E4C18C31BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F183C3-1634-421D-B7D2-C7EB2C215CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -754,9 +754,6 @@
     <t>Opposition seat share</t>
   </si>
   <si>
-    <t>Chamber Structure Leg.</t>
-  </si>
-  <si>
     <t>Number of legislative chambers</t>
   </si>
   <si>
@@ -878,6 +875,9 @@
   </si>
   <si>
     <t>per_chamber</t>
+  </si>
+  <si>
+    <t>Chamber Structure</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1272,7 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
@@ -1844,7 +1844,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>45</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>202</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>51</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>58</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>59</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>62</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>63</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>64</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>65</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>66</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>67</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>68</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>69</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>71</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>72</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>73</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>74</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>81</v>
       </c>
       <c r="B55" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C55" t="s">
         <v>219</v>
@@ -2975,7 +2975,7 @@
         <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C56" t="s">
         <v>220</v>
@@ -3010,7 +3010,7 @@
         <v>83</v>
       </c>
       <c r="B57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C57" t="s">
         <v>221</v>
@@ -3042,7 +3042,7 @@
         <v>84</v>
       </c>
       <c r="B58" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C58" t="s">
         <v>222</v>
@@ -3077,7 +3077,7 @@
         <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C59" t="s">
         <v>223</v>
@@ -3112,7 +3112,7 @@
         <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C60" t="s">
         <v>224</v>
@@ -3147,7 +3147,7 @@
         <v>87</v>
       </c>
       <c r="B61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" t="s">
         <v>225</v>
@@ -3182,7 +3182,7 @@
         <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C62" t="s">
         <v>226</v>
@@ -3217,7 +3217,7 @@
         <v>90</v>
       </c>
       <c r="B63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C63" t="s">
         <v>227</v>
@@ -3252,7 +3252,7 @@
         <v>91</v>
       </c>
       <c r="B64" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C64" t="s">
         <v>228</v>
@@ -3387,7 +3387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>95</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>96</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>97</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>98</v>
       </c>
@@ -3532,10 +3532,10 @@
         <v>99</v>
       </c>
       <c r="B72" t="s">
+        <v>284</v>
+      </c>
+      <c r="C72" t="s">
         <v>243</v>
-      </c>
-      <c r="C72" t="s">
-        <v>244</v>
       </c>
       <c r="D72" t="s">
         <v>46</v>
@@ -3570,10 +3570,10 @@
         <v>101</v>
       </c>
       <c r="B73" t="s">
+        <v>244</v>
+      </c>
+      <c r="C73" t="s">
         <v>245</v>
-      </c>
-      <c r="C73" t="s">
-        <v>246</v>
       </c>
       <c r="D73" t="s">
         <v>46</v>
@@ -3608,10 +3608,10 @@
         <v>102</v>
       </c>
       <c r="B74" t="s">
+        <v>246</v>
+      </c>
+      <c r="C74" t="s">
         <v>247</v>
-      </c>
-      <c r="C74" t="s">
-        <v>248</v>
       </c>
       <c r="D74" t="s">
         <v>46</v>
@@ -3640,10 +3640,10 @@
         <v>103</v>
       </c>
       <c r="B75" t="s">
+        <v>248</v>
+      </c>
+      <c r="C75" t="s">
         <v>249</v>
-      </c>
-      <c r="C75" t="s">
-        <v>250</v>
       </c>
       <c r="D75" t="s">
         <v>46</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>250</v>
+      </c>
+      <c r="B76" t="s">
         <v>251</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>252</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>253</v>
-      </c>
-      <c r="D76" t="s">
-        <v>254</v>
       </c>
       <c r="E76" t="s">
         <v>210</v>
       </c>
       <c r="F76" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -3701,22 +3701,22 @@
     </row>
     <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>255</v>
+      </c>
+      <c r="B77" t="s">
+        <v>279</v>
+      </c>
+      <c r="C77" t="s">
         <v>256</v>
       </c>
-      <c r="B77" t="s">
-        <v>280</v>
-      </c>
-      <c r="C77" t="s">
-        <v>257</v>
-      </c>
       <c r="D77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E77" t="s">
         <v>210</v>
       </c>
       <c r="F77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3733,16 +3733,16 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>257</v>
+      </c>
+      <c r="B78" t="s">
         <v>258</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>259</v>
       </c>
-      <c r="C78" t="s">
-        <v>260</v>
-      </c>
       <c r="D78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E78" t="s">
         <v>210</v>
@@ -3768,22 +3768,22 @@
     </row>
     <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>260</v>
+      </c>
+      <c r="B79" t="s">
+        <v>280</v>
+      </c>
+      <c r="C79" t="s">
         <v>261</v>
       </c>
-      <c r="B79" t="s">
-        <v>281</v>
-      </c>
-      <c r="C79" t="s">
-        <v>262</v>
-      </c>
       <c r="D79" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E79" t="s">
         <v>210</v>
       </c>
       <c r="F79" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3800,16 +3800,16 @@
     </row>
     <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>262</v>
+      </c>
+      <c r="B80" t="s">
+        <v>281</v>
+      </c>
+      <c r="C80" t="s">
         <v>263</v>
       </c>
-      <c r="B80" t="s">
-        <v>282</v>
-      </c>
-      <c r="C80" t="s">
-        <v>264</v>
-      </c>
       <c r="D80" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E80" t="s">
         <v>210</v>
@@ -3832,22 +3832,22 @@
     </row>
     <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>264</v>
+      </c>
+      <c r="B81" t="s">
+        <v>282</v>
+      </c>
+      <c r="C81" t="s">
         <v>265</v>
       </c>
-      <c r="B81" t="s">
-        <v>283</v>
-      </c>
-      <c r="C81" t="s">
-        <v>266</v>
-      </c>
       <c r="D81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E81" t="s">
         <v>210</v>
       </c>
       <c r="F81" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3864,22 +3864,22 @@
     </row>
     <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>266</v>
+      </c>
+      <c r="B82" t="s">
         <v>267</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>268</v>
       </c>
-      <c r="C82" t="s">
-        <v>269</v>
-      </c>
       <c r="D82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E82" t="s">
         <v>210</v>
       </c>
       <c r="F82" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3898,7 +3898,6 @@
   <autoFilter ref="A1:J82" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="4">
       <filters>
-        <filter val="SEED"/>
         <filter val="SLED"/>
       </filters>
     </filterColumn>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F183C3-1634-421D-B7D2-C7EB2C215CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F8F26E-B32F-4E76-AE3F-D10212E422D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="289">
   <si>
     <t>variable</t>
   </si>
@@ -292,9 +292,6 @@
     <t>margin_victory_sub_leg</t>
   </si>
   <si>
-    <t>#90A4AE,#00E5FF</t>
-  </si>
-  <si>
     <t>cumulative_electoral_year_sub_leg</t>
   </si>
   <si>
@@ -325,9 +322,6 @@
     <t>chamber_sub_leg</t>
   </si>
   <si>
-    <t>#d73027,#4575b4</t>
-  </si>
-  <si>
     <t>term_length_in_years_sub_leg</t>
   </si>
   <si>
@@ -878,6 +872,24 @@
   </si>
   <si>
     <t>Chamber Structure</t>
+  </si>
+  <si>
+    <t>chamber</t>
+  </si>
+  <si>
+    <t>renewal</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>#00ACC1,#FBC02D</t>
+  </si>
+  <si>
+    <t>#E57373,#FBC02D,#81C784,#BA68C8</t>
+  </si>
+  <si>
+    <t>#F08A5D,#B8DE6F</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1266,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -1272,7 +1284,7 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
@@ -1283,7 +1295,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1309,7 +1321,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1335,7 +1347,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1361,7 +1373,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1384,16 +1396,16 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -1413,16 +1425,16 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F7" t="s">
         <v>27</v>
@@ -1445,16 +1457,16 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F8" t="s">
         <v>30</v>
@@ -1474,16 +1486,16 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -1506,16 +1518,16 @@
         <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -1538,16 +1550,16 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
@@ -1570,16 +1582,16 @@
         <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -1599,16 +1611,16 @@
         <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -1628,19 +1640,19 @@
     </row>
     <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
@@ -1660,19 +1672,19 @@
     </row>
     <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -1692,22 +1704,22 @@
         <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F16" t="s">
         <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1724,16 +1736,16 @@
         <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
@@ -1750,19 +1762,19 @@
     </row>
     <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
@@ -1785,16 +1797,16 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
@@ -1817,16 +1829,16 @@
         <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
@@ -1849,16 +1861,16 @@
         <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D21" t="s">
         <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -1878,19 +1890,19 @@
     </row>
     <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D22" t="s">
         <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F22" t="s">
         <v>34</v>
@@ -1910,19 +1922,19 @@
     </row>
     <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
@@ -1945,16 +1957,16 @@
         <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -1971,19 +1983,19 @@
     </row>
     <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -2006,16 +2018,16 @@
         <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
@@ -2035,19 +2047,19 @@
     </row>
     <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
@@ -2070,16 +2082,16 @@
         <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
@@ -2102,16 +2114,16 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D29" t="s">
         <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -2134,16 +2146,16 @@
         <v>51</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>16</v>
@@ -2161,21 +2173,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -2198,16 +2210,16 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
@@ -2230,16 +2242,16 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D33" t="s">
         <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
@@ -2262,16 +2274,16 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D34" t="s">
         <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
@@ -2291,16 +2303,16 @@
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D35" t="s">
         <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
@@ -2323,16 +2335,16 @@
         <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
@@ -2355,16 +2367,16 @@
         <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D37" t="s">
         <v>46</v>
       </c>
       <c r="E37" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F37" t="s">
         <v>60</v>
@@ -2387,16 +2399,16 @@
         <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
@@ -2419,16 +2431,16 @@
         <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D39" t="s">
         <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F39" t="s">
         <v>60</v>
@@ -2451,16 +2463,16 @@
         <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D40" t="s">
         <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
@@ -2483,16 +2495,16 @@
         <v>65</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>60</v>
@@ -2515,16 +2527,16 @@
         <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D42" t="s">
         <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -2547,16 +2559,16 @@
         <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D43" t="s">
         <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F43" t="s">
         <v>60</v>
@@ -2579,16 +2591,16 @@
         <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D44" t="s">
         <v>46</v>
       </c>
       <c r="E44" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
@@ -2611,16 +2623,16 @@
         <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D45" t="s">
         <v>46</v>
       </c>
       <c r="E45" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F45" t="s">
         <v>60</v>
@@ -2643,16 +2655,16 @@
         <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D46" t="s">
         <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
@@ -2675,16 +2687,16 @@
         <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D47" t="s">
         <v>46</v>
       </c>
       <c r="E47" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F47" t="s">
         <v>60</v>
@@ -2707,16 +2719,16 @@
         <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D48" t="s">
         <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F48" t="s">
         <v>60</v>
@@ -2739,16 +2751,16 @@
         <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D49" t="s">
         <v>46</v>
       </c>
       <c r="E49" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
@@ -2771,16 +2783,16 @@
         <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D50" t="s">
         <v>46</v>
       </c>
       <c r="E50" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F50" t="s">
         <v>75</v>
@@ -2803,16 +2815,16 @@
         <v>76</v>
       </c>
       <c r="B51" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D51" t="s">
         <v>77</v>
       </c>
       <c r="E51" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
@@ -2830,21 +2842,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>78</v>
       </c>
       <c r="B52" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C52" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D52" t="s">
         <v>46</v>
       </c>
       <c r="E52" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
@@ -2865,21 +2877,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>79</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C53" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D53" t="s">
         <v>46</v>
       </c>
       <c r="E53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
@@ -2900,21 +2912,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C54" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D54" t="s">
         <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F54" t="s">
         <v>60</v>
@@ -2935,21 +2947,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>81</v>
       </c>
       <c r="B55" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D55" t="s">
         <v>46</v>
       </c>
       <c r="E55" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
@@ -2970,21 +2982,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C56" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D56" t="s">
         <v>46</v>
       </c>
       <c r="E56" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F56" t="s">
         <v>60</v>
@@ -3010,16 +3022,16 @@
         <v>83</v>
       </c>
       <c r="B57" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C57" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D57" t="s">
         <v>46</v>
       </c>
       <c r="E57" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F57" t="s">
         <v>25</v>
@@ -3042,16 +3054,16 @@
         <v>84</v>
       </c>
       <c r="B58" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C58" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D58" t="s">
         <v>46</v>
       </c>
       <c r="E58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F58" t="s">
         <v>16</v>
@@ -3077,16 +3089,16 @@
         <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C59" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D59" t="s">
         <v>46</v>
       </c>
       <c r="E59" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -3112,16 +3124,16 @@
         <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C60" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D60" t="s">
         <v>46</v>
       </c>
       <c r="E60" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -3147,16 +3159,16 @@
         <v>87</v>
       </c>
       <c r="B61" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C61" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D61" t="s">
         <v>46</v>
       </c>
       <c r="E61" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -3182,16 +3194,16 @@
         <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C62" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D62" t="s">
         <v>46</v>
       </c>
       <c r="E62" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F62" t="s">
         <v>60</v>
@@ -3212,21 +3224,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B63" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C63" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D63" t="s">
         <v>46</v>
       </c>
       <c r="E63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>16</v>
@@ -3249,25 +3261,25 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B64" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C64" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D64" t="s">
         <v>46</v>
       </c>
       <c r="E64" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F64" t="s">
         <v>34</v>
       </c>
       <c r="G64" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -3282,21 +3294,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B65" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C65" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D65" t="s">
         <v>46</v>
       </c>
       <c r="E65" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>16</v>
@@ -3317,21 +3329,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B66" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C66" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D66" t="s">
         <v>46</v>
       </c>
       <c r="E66" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>16</v>
@@ -3352,21 +3364,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B67" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C67" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D67" t="s">
         <v>46</v>
       </c>
       <c r="E67" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>16</v>
@@ -3389,19 +3401,19 @@
     </row>
     <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B68" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C68" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D68" t="s">
         <v>46</v>
       </c>
       <c r="E68" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>16</v>
@@ -3424,19 +3436,19 @@
     </row>
     <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B69" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C69" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D69" t="s">
         <v>46</v>
       </c>
       <c r="E69" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F69" t="s">
         <v>60</v>
@@ -3459,19 +3471,19 @@
     </row>
     <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B70" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C70" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D70" t="s">
         <v>46</v>
       </c>
       <c r="E70" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>16</v>
@@ -3494,19 +3506,19 @@
     </row>
     <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B71" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C71" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D71" t="s">
         <v>46</v>
       </c>
       <c r="E71" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F71" t="s">
         <v>60</v>
@@ -3527,59 +3539,59 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72" t="s">
+        <v>282</v>
+      </c>
+      <c r="C72" t="s">
+        <v>241</v>
+      </c>
+      <c r="D72" t="s">
+        <v>46</v>
+      </c>
+      <c r="E72" t="s">
+        <v>208</v>
+      </c>
+      <c r="F72" t="s">
+        <v>283</v>
+      </c>
+      <c r="G72" t="s">
+        <v>286</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72" t="s">
+        <v>20</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>99</v>
       </c>
-      <c r="B72" t="s">
-        <v>284</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="B73" t="s">
+        <v>242</v>
+      </c>
+      <c r="C73" t="s">
         <v>243</v>
       </c>
-      <c r="D72" t="s">
-        <v>46</v>
-      </c>
-      <c r="E72" t="s">
-        <v>210</v>
-      </c>
-      <c r="F72" t="s">
-        <v>12</v>
-      </c>
-      <c r="G72" t="s">
-        <v>100</v>
-      </c>
-      <c r="H72">
-        <v>1</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72" t="s">
-        <v>20</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>101</v>
-      </c>
-      <c r="B73" t="s">
-        <v>244</v>
-      </c>
-      <c r="C73" t="s">
-        <v>245</v>
-      </c>
       <c r="D73" t="s">
         <v>46</v>
       </c>
       <c r="E73" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>16</v>
@@ -3603,56 +3615,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B74" t="s">
+        <v>244</v>
+      </c>
+      <c r="C74" t="s">
+        <v>245</v>
+      </c>
+      <c r="D74" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74" t="s">
+        <v>208</v>
+      </c>
+      <c r="F74" t="s">
+        <v>284</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74" t="s">
+        <v>20</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>101</v>
+      </c>
+      <c r="B75" t="s">
         <v>246</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C75" t="s">
         <v>247</v>
       </c>
-      <c r="D74" t="s">
-        <v>46</v>
-      </c>
-      <c r="E74" t="s">
-        <v>210</v>
-      </c>
-      <c r="F74" t="s">
-        <v>12</v>
-      </c>
-      <c r="H74">
-        <v>1</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
-        <v>20</v>
-      </c>
-      <c r="K74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>103</v>
-      </c>
-      <c r="B75" t="s">
-        <v>248</v>
-      </c>
-      <c r="C75" t="s">
-        <v>249</v>
-      </c>
       <c r="D75" t="s">
         <v>46</v>
       </c>
       <c r="E75" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F75" t="s">
-        <v>12</v>
+        <v>285</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -3669,22 +3687,22 @@
     </row>
     <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>248</v>
+      </c>
+      <c r="B76" t="s">
+        <v>249</v>
+      </c>
+      <c r="C76" t="s">
         <v>250</v>
       </c>
-      <c r="B76" t="s">
+      <c r="D76" t="s">
         <v>251</v>
       </c>
-      <c r="C76" t="s">
+      <c r="E76" t="s">
+        <v>208</v>
+      </c>
+      <c r="F76" t="s">
         <v>252</v>
-      </c>
-      <c r="D76" t="s">
-        <v>253</v>
-      </c>
-      <c r="E76" t="s">
-        <v>210</v>
-      </c>
-      <c r="F76" t="s">
-        <v>254</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -3701,51 +3719,51 @@
     </row>
     <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>253</v>
+      </c>
+      <c r="B77" t="s">
+        <v>277</v>
+      </c>
+      <c r="C77" t="s">
+        <v>254</v>
+      </c>
+      <c r="D77" t="s">
+        <v>251</v>
+      </c>
+      <c r="E77" t="s">
+        <v>208</v>
+      </c>
+      <c r="F77" t="s">
+        <v>252</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77" t="s">
+        <v>20</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>255</v>
       </c>
-      <c r="B77" t="s">
-        <v>279</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="B78" t="s">
         <v>256</v>
       </c>
-      <c r="D77" t="s">
-        <v>253</v>
-      </c>
-      <c r="E77" t="s">
-        <v>210</v>
-      </c>
-      <c r="F77" t="s">
-        <v>254</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77" t="s">
-        <v>20</v>
-      </c>
-      <c r="K77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="C78" t="s">
         <v>257</v>
       </c>
-      <c r="B78" t="s">
-        <v>258</v>
-      </c>
-      <c r="C78" t="s">
-        <v>259</v>
-      </c>
       <c r="D78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E78" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F78" t="s">
         <v>75</v>
@@ -3768,22 +3786,22 @@
     </row>
     <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B79" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C79" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D79" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E79" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F79" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3800,19 +3818,19 @@
     </row>
     <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B80" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C80" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D80" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E80" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F80" t="s">
         <v>30</v>
@@ -3832,22 +3850,22 @@
     </row>
     <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B81" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C81" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D81" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E81" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F81" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3864,22 +3882,22 @@
     </row>
     <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>264</v>
+      </c>
+      <c r="B82" t="s">
+        <v>265</v>
+      </c>
+      <c r="C82" t="s">
         <v>266</v>
       </c>
-      <c r="B82" t="s">
-        <v>267</v>
-      </c>
-      <c r="C82" t="s">
-        <v>268</v>
-      </c>
       <c r="D82" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E82" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F82" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3896,9 +3914,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J82" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
+    <filterColumn colId="1">
       <filters>
-        <filter val="SLED"/>
+        <filter val="Concurrent Elections"/>
+        <filter val="Concurrent with National Election Leg."/>
       </filters>
     </filterColumn>
     <filterColumn colId="7">

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9FC079-BB8B-4573-A580-C03B56AEA288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E72B39-D40A-4653-9743-9C67D430C42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$J$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$J$88</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="393">
   <si>
     <t>variable</t>
   </si>
@@ -1133,6 +1133,75 @@
   </si>
   <si>
     <t>seats as % of total contested</t>
+  </si>
+  <si>
+    <t>SUR_index_giraudy_2015</t>
+  </si>
+  <si>
+    <t>SUR_index_sub_exe</t>
+  </si>
+  <si>
+    <t>contestation_sub_exe</t>
+  </si>
+  <si>
+    <t>contestation_sub_leg</t>
+  </si>
+  <si>
+    <t>turnover_sub_exe</t>
+  </si>
+  <si>
+    <t>clean_elections_sub_exe_giraudy_2015</t>
+  </si>
+  <si>
+    <t>SUR Index 2015</t>
+  </si>
+  <si>
+    <t>the level of subnational democracy</t>
+  </si>
+  <si>
+    <t>the level of subnational democracy in the executive branch</t>
+  </si>
+  <si>
+    <t>SUR Index</t>
+  </si>
+  <si>
+    <t>Subnational Contestation</t>
+  </si>
+  <si>
+    <t>Subnational Contestation leg.</t>
+  </si>
+  <si>
+    <t>Average Turnover</t>
+  </si>
+  <si>
+    <t>Index of Post-electoral Conflict</t>
+  </si>
+  <si>
+    <t>Democracy Indices</t>
+  </si>
+  <si>
+    <t>the level of subnational contestation</t>
+  </si>
+  <si>
+    <t>the level of subnational leg. contestation</t>
+  </si>
+  <si>
+    <t>the average of governor and party turnover</t>
+  </si>
+  <si>
+    <t>the index of Post-electoral Conflict</t>
+  </si>
+  <si>
+    <t>#FDE0DD,#FBB4B9,#F768A1,#C51B8A</t>
+  </si>
+  <si>
+    <t>#F2F2F7,#D9E0EE,#AEB8D0,#7A86A2</t>
+  </si>
+  <si>
+    <t>#F4E6F8,#E0C2F0,#C08AE0,#8C4CB8</t>
+  </si>
+  <si>
+    <t>#F2F8FE,#CFE3F5,#9BC4E2,#5A9BCF</t>
   </si>
 </sst>
 </file>
@@ -1492,22 +1561,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K82"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K88"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1542,219 +1611,198 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3" t="s">
+        <v>392</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E4" t="s">
+        <v>384</v>
+      </c>
+      <c r="F4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" t="s">
+        <v>391</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E5" t="s">
+        <v>384</v>
+      </c>
+      <c r="F5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" t="s">
+        <v>391</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7" t="s">
+        <v>383</v>
+      </c>
+      <c r="E7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" t="s">
+        <v>389</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D8" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E8" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F8" t="s">
         <v>15</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1766,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
@@ -1788,9 +1836,6 @@
       <c r="F9" t="s">
         <v>20</v>
       </c>
-      <c r="G9" t="s">
-        <v>47</v>
-      </c>
       <c r="H9">
         <v>0</v>
       </c>
@@ -1798,91 +1843,85 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
       <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
         <v>25</v>
       </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
       <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -1891,7 +1930,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1903,18 +1942,18 @@
         <v>16</v>
       </c>
       <c r="K12" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
@@ -1923,10 +1962,10 @@
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1938,33 +1977,30 @@
         <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1973,27 +2009,30 @@
         <v>16</v>
       </c>
       <c r="K14" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2002,33 +2041,33 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K15" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2037,65 +2076,65 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K16" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>51</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K17" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
         <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2104,106 +2143,103 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K18" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
         <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
       </c>
       <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
         <v>25</v>
-      </c>
-      <c r="F20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" t="s">
-        <v>89</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2212,30 +2248,30 @@
         <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G22" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -2247,33 +2283,30 @@
         <v>26</v>
       </c>
       <c r="K22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -2282,18 +2315,18 @@
         <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
         <v>25</v>
@@ -2302,10 +2335,13 @@
         <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>51</v>
+      </c>
+      <c r="G24" t="s">
+        <v>52</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2314,18 +2350,18 @@
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
         <v>25</v>
@@ -2334,10 +2370,10 @@
         <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2349,18 +2385,18 @@
         <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
         <v>25</v>
@@ -2378,71 +2414,71 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="s">
         <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s">
         <v>25</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="s">
         <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
         <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -2454,101 +2490,98 @@
         <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
         <v>51</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G31" t="s">
         <v>52</v>
       </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
-        <v>26</v>
-      </c>
-      <c r="K29" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>178</v>
-      </c>
-      <c r="B30" t="s">
-        <v>179</v>
-      </c>
-      <c r="C30" t="s">
-        <v>180</v>
-      </c>
-      <c r="D30" t="s">
-        <v>89</v>
-      </c>
-      <c r="E30" t="s">
-        <v>117</v>
-      </c>
-      <c r="F30" t="s">
-        <v>181</v>
-      </c>
-      <c r="G30" t="s">
-        <v>133</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>26</v>
-      </c>
-      <c r="K30" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B31" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" t="s">
-        <v>116</v>
-      </c>
-      <c r="D31" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" t="s">
-        <v>117</v>
-      </c>
-      <c r="F31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" t="s">
-        <v>47</v>
-      </c>
       <c r="H31">
         <v>0</v>
       </c>
@@ -2559,18 +2592,18 @@
         <v>26</v>
       </c>
       <c r="K31" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s">
         <v>25</v>
@@ -2579,33 +2612,33 @@
         <v>25</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="s">
         <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
         <v>25</v>
@@ -2614,45 +2647,45 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="s">
         <v>26</v>
       </c>
       <c r="K33" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G34" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2664,18 +2697,18 @@
         <v>26</v>
       </c>
       <c r="K34" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D35" t="s">
         <v>89</v>
@@ -2684,7 +2717,10 @@
         <v>42</v>
       </c>
       <c r="F35" t="s">
-        <v>43</v>
+        <v>51</v>
+      </c>
+      <c r="G35" t="s">
+        <v>52</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2696,18 +2732,18 @@
         <v>26</v>
       </c>
       <c r="K35" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="D36" t="s">
         <v>89</v>
@@ -2716,7 +2752,7 @@
         <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="G36" t="s">
         <v>133</v>
@@ -2731,18 +2767,18 @@
         <v>26</v>
       </c>
       <c r="K36" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="D37" t="s">
         <v>89</v>
@@ -2754,100 +2790,100 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="s">
         <v>26</v>
       </c>
       <c r="K37" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="B38" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="s">
         <v>26</v>
       </c>
       <c r="K38" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="C39" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G39" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="s">
         <v>26</v>
       </c>
       <c r="K39" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="D40" t="s">
         <v>89</v>
@@ -2856,68 +2892,65 @@
         <v>117</v>
       </c>
       <c r="F40" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="s">
         <v>26</v>
       </c>
       <c r="K40" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="D41" t="s">
         <v>89</v>
       </c>
       <c r="E41" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="s">
         <v>26</v>
       </c>
       <c r="K41" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
         <v>89</v>
@@ -2926,10 +2959,10 @@
         <v>117</v>
       </c>
       <c r="F42" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="G42" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -2941,18 +2974,18 @@
         <v>26</v>
       </c>
       <c r="K42" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
         <v>89</v>
@@ -2976,18 +3009,18 @@
         <v>26</v>
       </c>
       <c r="K43" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="B44" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
         <v>89</v>
@@ -3011,18 +3044,18 @@
         <v>26</v>
       </c>
       <c r="K44" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s">
         <v>89</v>
@@ -3046,18 +3079,18 @@
         <v>26</v>
       </c>
       <c r="K45" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D46" t="s">
         <v>89</v>
@@ -3081,18 +3114,18 @@
         <v>26</v>
       </c>
       <c r="K46" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B47" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C47" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D47" t="s">
         <v>89</v>
@@ -3116,18 +3149,18 @@
         <v>26</v>
       </c>
       <c r="K47" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D48" t="s">
         <v>89</v>
@@ -3151,18 +3184,18 @@
         <v>26</v>
       </c>
       <c r="K48" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="D49" t="s">
         <v>89</v>
@@ -3171,7 +3204,7 @@
         <v>117</v>
       </c>
       <c r="F49" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="G49" t="s">
         <v>133</v>
@@ -3186,18 +3219,18 @@
         <v>26</v>
       </c>
       <c r="K49" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B50" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="C50" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="D50" t="s">
         <v>89</v>
@@ -3206,77 +3239,80 @@
         <v>117</v>
       </c>
       <c r="F50" t="s">
+        <v>140</v>
+      </c>
+      <c r="G50" t="s">
+        <v>141</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50" t="s">
+        <v>26</v>
+      </c>
+      <c r="K50" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51" t="s">
+        <v>161</v>
+      </c>
+      <c r="C51" t="s">
+        <v>162</v>
+      </c>
+      <c r="D51" t="s">
+        <v>89</v>
+      </c>
+      <c r="E51" t="s">
+        <v>117</v>
+      </c>
+      <c r="F51" t="s">
         <v>20</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G51" t="s">
         <v>133</v>
       </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-      <c r="J50" t="s">
-        <v>26</v>
-      </c>
-      <c r="K50" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>182</v>
-      </c>
-      <c r="B51" t="s">
-        <v>183</v>
-      </c>
-      <c r="C51" t="s">
-        <v>184</v>
-      </c>
-      <c r="D51" t="s">
-        <v>185</v>
-      </c>
-      <c r="E51" t="s">
-        <v>186</v>
-      </c>
-      <c r="F51" t="s">
-        <v>15</v>
-      </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="s">
         <v>26</v>
       </c>
       <c r="K51" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>273</v>
+        <v>163</v>
       </c>
       <c r="B52" t="s">
-        <v>274</v>
+        <v>164</v>
       </c>
       <c r="C52" t="s">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="D52" t="s">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c r="E52" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="F52" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="G52" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -3288,24 +3324,24 @@
         <v>26</v>
       </c>
       <c r="K52" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="B53" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="C53" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="D53" t="s">
         <v>89</v>
       </c>
       <c r="E53" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="F53" t="s">
         <v>20</v>
@@ -3323,30 +3359,30 @@
         <v>26</v>
       </c>
       <c r="K53" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B54" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C54" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D54" t="s">
         <v>89</v>
       </c>
       <c r="E54" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="G54" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -3358,30 +3394,30 @@
         <v>26</v>
       </c>
       <c r="K54" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="B55" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="D55" t="s">
         <v>89</v>
       </c>
       <c r="E55" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="F55" t="s">
         <v>140</v>
       </c>
       <c r="G55" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -3393,24 +3429,24 @@
         <v>26</v>
       </c>
       <c r="K55" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="B56" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="C56" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="D56" t="s">
         <v>89</v>
       </c>
       <c r="E56" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="F56" t="s">
         <v>20</v>
@@ -3428,85 +3464,85 @@
         <v>26</v>
       </c>
       <c r="K56" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="B57" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="C57" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="D57" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="E57" t="s">
         <v>186</v>
       </c>
       <c r="F57" t="s">
-        <v>140</v>
-      </c>
-      <c r="G57" t="s">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="s">
         <v>26</v>
       </c>
       <c r="K57" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>202</v>
+        <v>273</v>
       </c>
       <c r="B58" t="s">
-        <v>203</v>
+        <v>274</v>
       </c>
       <c r="C58" t="s">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="D58" t="s">
-        <v>89</v>
+        <v>268</v>
       </c>
       <c r="E58" t="s">
         <v>186</v>
       </c>
       <c r="F58" t="s">
-        <v>33</v>
+        <v>181</v>
+      </c>
+      <c r="G58" t="s">
+        <v>133</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="s">
         <v>26</v>
       </c>
       <c r="K58" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="B59" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="C59" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="D59" t="s">
         <v>89</v>
@@ -3521,27 +3557,27 @@
         <v>133</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="s">
         <v>26</v>
       </c>
       <c r="K59" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B60" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C60" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="D60" t="s">
         <v>89</v>
@@ -3556,27 +3592,27 @@
         <v>133</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="s">
         <v>26</v>
       </c>
       <c r="K60" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="B61" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="C61" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="D61" t="s">
         <v>89</v>
@@ -3585,33 +3621,33 @@
         <v>186</v>
       </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="G61" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="s">
         <v>26</v>
       </c>
       <c r="K61" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B62" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="C62" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D62" t="s">
         <v>89</v>
@@ -3626,27 +3662,27 @@
         <v>133</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="s">
         <v>26</v>
       </c>
       <c r="K62" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B63" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="C63" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D63" t="s">
         <v>89</v>
@@ -3661,27 +3697,27 @@
         <v>141</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="s">
         <v>26</v>
       </c>
       <c r="K63" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B64" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C64" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="D64" t="s">
         <v>89</v>
@@ -3690,33 +3726,30 @@
         <v>186</v>
       </c>
       <c r="F64" t="s">
-        <v>20</v>
-      </c>
-      <c r="G64" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="s">
         <v>26</v>
       </c>
       <c r="K64" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="B65" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C65" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="D65" t="s">
         <v>89</v>
@@ -3725,13 +3758,13 @@
         <v>186</v>
       </c>
       <c r="F65" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G65" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3740,18 +3773,18 @@
         <v>26</v>
       </c>
       <c r="K65" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="B66" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="C66" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="D66" t="s">
         <v>89</v>
@@ -3763,30 +3796,30 @@
         <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="s">
         <v>26</v>
       </c>
       <c r="K66" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="B67" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="C67" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="D67" t="s">
         <v>89</v>
@@ -3798,30 +3831,30 @@
         <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="s">
         <v>26</v>
       </c>
       <c r="K67" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="B68" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="C68" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="D68" t="s">
         <v>89</v>
@@ -3833,10 +3866,10 @@
         <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3845,18 +3878,18 @@
         <v>26</v>
       </c>
       <c r="K68" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="B69" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="C69" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="D69" t="s">
         <v>89</v>
@@ -3865,10 +3898,10 @@
         <v>186</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="G69" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -3880,18 +3913,18 @@
         <v>26</v>
       </c>
       <c r="K69" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="B70" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="C70" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D70" t="s">
         <v>89</v>
@@ -3900,33 +3933,33 @@
         <v>186</v>
       </c>
       <c r="F70" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="G70" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="s">
         <v>26</v>
       </c>
       <c r="K70" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="B71" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C71" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="D71" t="s">
         <v>89</v>
@@ -3935,13 +3968,13 @@
         <v>186</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G71" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3950,18 +3983,18 @@
         <v>26</v>
       </c>
       <c r="K71" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B72" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="C72" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D72" t="s">
         <v>89</v>
@@ -3970,33 +4003,33 @@
         <v>186</v>
       </c>
       <c r="F72" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="G72" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="s">
         <v>26</v>
       </c>
       <c r="K72" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="B73" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="C73" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="D73" t="s">
         <v>89</v>
@@ -4005,33 +4038,33 @@
         <v>186</v>
       </c>
       <c r="F73" t="s">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="G73" t="s">
-        <v>251</v>
+        <v>47</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="s">
         <v>26</v>
       </c>
       <c r="K73" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B74" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="C74" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="D74" t="s">
         <v>89</v>
@@ -4049,24 +4082,24 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="s">
         <v>26</v>
       </c>
       <c r="K74" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B75" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="C75" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="D75" t="s">
         <v>89</v>
@@ -4075,13 +4108,13 @@
         <v>186</v>
       </c>
       <c r="F75" t="s">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>259</v>
+        <v>47</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -4090,18 +4123,18 @@
         <v>26</v>
       </c>
       <c r="K75" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="B76" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="D76" t="s">
         <v>89</v>
@@ -4110,13 +4143,13 @@
         <v>186</v>
       </c>
       <c r="F76" t="s">
-        <v>263</v>
+        <v>140</v>
       </c>
       <c r="G76" t="s">
-        <v>264</v>
+        <v>141</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -4125,27 +4158,30 @@
         <v>26</v>
       </c>
       <c r="K76" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="B77" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="C77" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="D77" t="s">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c r="E77" t="s">
         <v>186</v>
       </c>
       <c r="F77" t="s">
-        <v>269</v>
+        <v>20</v>
+      </c>
+      <c r="G77" t="s">
+        <v>47</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -4157,27 +4193,30 @@
         <v>26</v>
       </c>
       <c r="K77" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="B78" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="C78" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="D78" t="s">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c r="E78" t="s">
         <v>186</v>
       </c>
       <c r="F78" t="s">
-        <v>269</v>
+        <v>140</v>
+      </c>
+      <c r="G78" t="s">
+        <v>141</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -4189,30 +4228,33 @@
         <v>26</v>
       </c>
       <c r="K78" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="B79" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="C79" t="s">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="D79" t="s">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c r="E79" t="s">
         <v>186</v>
       </c>
       <c r="F79" t="s">
-        <v>269</v>
+        <v>250</v>
+      </c>
+      <c r="G79" t="s">
+        <v>251</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -4221,62 +4263,68 @@
         <v>26</v>
       </c>
       <c r="K79" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="B80" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="C80" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="D80" t="s">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c r="E80" t="s">
         <v>186</v>
       </c>
       <c r="F80" t="s">
-        <v>43</v>
+        <v>20</v>
+      </c>
+      <c r="G80" t="s">
+        <v>47</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="s">
         <v>26</v>
       </c>
       <c r="K80" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="B81" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="C81" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="D81" t="s">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c r="E81" t="s">
         <v>186</v>
       </c>
       <c r="F81" t="s">
-        <v>269</v>
+        <v>258</v>
+      </c>
+      <c r="G81" t="s">
+        <v>259</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -4285,43 +4333,238 @@
         <v>26</v>
       </c>
       <c r="K81" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="B82" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="C82" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="D82" t="s">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c r="E82" t="s">
         <v>186</v>
       </c>
       <c r="F82" t="s">
+        <v>263</v>
+      </c>
+      <c r="G82" t="s">
+        <v>264</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82" t="s">
+        <v>26</v>
+      </c>
+      <c r="K82" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>265</v>
+      </c>
+      <c r="B83" t="s">
+        <v>266</v>
+      </c>
+      <c r="C83" t="s">
+        <v>267</v>
+      </c>
+      <c r="D83" t="s">
+        <v>268</v>
+      </c>
+      <c r="E83" t="s">
+        <v>186</v>
+      </c>
+      <c r="F83" t="s">
         <v>269</v>
       </c>
-      <c r="H82">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82" t="s">
-        <v>26</v>
-      </c>
-      <c r="K82" t="s">
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83" t="s">
+        <v>26</v>
+      </c>
+      <c r="K83" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>270</v>
+      </c>
+      <c r="B84" t="s">
+        <v>271</v>
+      </c>
+      <c r="C84" t="s">
+        <v>272</v>
+      </c>
+      <c r="D84" t="s">
+        <v>268</v>
+      </c>
+      <c r="E84" t="s">
+        <v>186</v>
+      </c>
+      <c r="F84" t="s">
+        <v>269</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84" t="s">
+        <v>26</v>
+      </c>
+      <c r="K84" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>276</v>
+      </c>
+      <c r="B85" t="s">
+        <v>277</v>
+      </c>
+      <c r="C85" t="s">
+        <v>278</v>
+      </c>
+      <c r="D85" t="s">
+        <v>268</v>
+      </c>
+      <c r="E85" t="s">
+        <v>186</v>
+      </c>
+      <c r="F85" t="s">
+        <v>269</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85" t="s">
+        <v>26</v>
+      </c>
+      <c r="K85" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>279</v>
+      </c>
+      <c r="B86" t="s">
+        <v>280</v>
+      </c>
+      <c r="C86" t="s">
+        <v>281</v>
+      </c>
+      <c r="D86" t="s">
+        <v>268</v>
+      </c>
+      <c r="E86" t="s">
+        <v>186</v>
+      </c>
+      <c r="F86" t="s">
+        <v>43</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86" t="s">
+        <v>26</v>
+      </c>
+      <c r="K86" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>282</v>
+      </c>
+      <c r="B87" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" t="s">
+        <v>284</v>
+      </c>
+      <c r="D87" t="s">
+        <v>268</v>
+      </c>
+      <c r="E87" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" t="s">
+        <v>269</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
+        <v>26</v>
+      </c>
+      <c r="K87" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>285</v>
+      </c>
+      <c r="B88" t="s">
+        <v>286</v>
+      </c>
+      <c r="C88" t="s">
+        <v>287</v>
+      </c>
+      <c r="D88" t="s">
+        <v>268</v>
+      </c>
+      <c r="E88" t="s">
+        <v>186</v>
+      </c>
+      <c r="F88" t="s">
+        <v>269</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K88" t="s">
         <v>369</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J82" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J88" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC1DF1A-62DB-4BC5-9E6B-5F09EB19BC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B48CEC-7BB9-45AA-A835-DE6B91B3D36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="317">
   <si>
     <t>variable</t>
   </si>
@@ -956,6 +956,24 @@
   </si>
   <si>
     <t>Leg. Elections Concurrent with Nat. Elections</t>
+  </si>
+  <si>
+    <t>add_indices</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Higher values indicate cleaner elections at the subnational executive level, reflecting lower post-electoral conflict.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Higher values indicate higher levels of subnational legistlative competitiveness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Higher values indicate higher levels of subnational executive competitiveness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Higher values indicate higher levels of subnational democracy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Higher values indicate higher levels of subnational executive turnover.</t>
   </si>
 </sst>
 </file>
@@ -1330,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.42578125" bestFit="1" customWidth="1"/>
@@ -1344,7 +1362,7 @@
     <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1375,8 +1393,11 @@
       <c r="J1" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>267</v>
       </c>
@@ -1404,8 +1425,11 @@
       <c r="J2" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>268</v>
       </c>
@@ -1433,8 +1457,11 @@
       <c r="J3" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>269</v>
       </c>
@@ -1462,8 +1489,11 @@
       <c r="J4" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>270</v>
       </c>
@@ -1491,8 +1521,11 @@
       <c r="J5" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>271</v>
       </c>
@@ -1520,8 +1553,11 @@
       <c r="J6" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>272</v>
       </c>
@@ -1549,8 +1585,11 @@
       <c r="J7" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1579,7 +1618,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1608,7 +1647,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1637,7 +1676,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1666,7 +1705,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1695,7 +1734,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1727,7 +1766,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1756,7 +1795,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1788,7 +1827,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>39</v>
       </c>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B48CEC-7BB9-45AA-A835-DE6B91B3D36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B761E4-7A32-477A-B922-D4DD6BD1716C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -871,9 +871,6 @@
     <t>#FDE0DD,#FBB4B9,#F768A1,#C51B8A</t>
   </si>
   <si>
-    <t>#F2F2F7,#D9E0EE,#AEB8D0,#7A86A2</t>
-  </si>
-  <si>
     <t>#F4E6F8,#E0C2F0,#C08AE0,#8C4CB8</t>
   </si>
   <si>
@@ -973,7 +970,10 @@
     <t xml:space="preserve"> Higher values indicate higher levels of subnational democracy.</t>
   </si>
   <si>
-    <t xml:space="preserve"> Higher values indicate higher levels of subnational executive turnover.</t>
+    <t>#C0D2EB,#4257A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Higher values indicate higher subnational executive turnover.</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1394,7 @@
         <v>187</v>
       </c>
       <c r="K1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1402,7 +1402,7 @@
         <v>267</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D2" t="s">
         <v>276</v>
@@ -1411,7 +1411,7 @@
         <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1426,7 +1426,7 @@
         <v>273</v>
       </c>
       <c r="K2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
         <v>121</v>
       </c>
       <c r="F3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>274</v>
       </c>
       <c r="K3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1466,7 +1466,7 @@
         <v>269</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D4" t="s">
         <v>276</v>
@@ -1475,7 +1475,7 @@
         <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1490,7 +1490,7 @@
         <v>277</v>
       </c>
       <c r="K4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,7 +1498,7 @@
         <v>270</v>
       </c>
       <c r="B5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D5" t="s">
         <v>276</v>
@@ -1507,7 +1507,7 @@
         <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>278</v>
       </c>
       <c r="K5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1530,7 +1530,7 @@
         <v>271</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D6" t="s">
         <v>276</v>
@@ -1539,7 +1539,7 @@
         <v>121</v>
       </c>
       <c r="F6" t="s">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1562,7 +1562,7 @@
         <v>272</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D7" t="s">
         <v>276</v>
@@ -1586,7 +1586,7 @@
         <v>280</v>
       </c>
       <c r="K7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2484,7 +2484,7 @@
         <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2492,7 +2492,7 @@
         <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C37" t="s">
         <v>68</v>
@@ -2524,7 +2524,7 @@
         <v>87</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C38" t="s">
         <v>21</v>
@@ -2556,7 +2556,7 @@
         <v>88</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C39" t="s">
         <v>21</v>
@@ -2713,7 +2713,7 @@
         <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C44" t="s">
         <v>68</v>
@@ -2777,7 +2777,7 @@
         <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C46" t="s">
         <v>68</v>
@@ -2841,7 +2841,7 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C48" t="s">
         <v>68</v>
@@ -2905,7 +2905,7 @@
         <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C50" t="s">
         <v>68</v>
@@ -2969,7 +2969,7 @@
         <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C52" t="s">
         <v>68</v>
@@ -3033,7 +3033,7 @@
         <v>115</v>
       </c>
       <c r="B54" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C54" t="s">
         <v>68</v>
@@ -3065,7 +3065,7 @@
         <v>116</v>
       </c>
       <c r="B55" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C55" t="s">
         <v>68</v>
@@ -3182,7 +3182,7 @@
         <v>22</v>
       </c>
       <c r="J58" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -3254,7 +3254,7 @@
         <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C61" t="s">
         <v>68</v>
@@ -3318,7 +3318,7 @@
         <v>133</v>
       </c>
       <c r="B63" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C63" t="s">
         <v>68</v>
@@ -3507,7 +3507,7 @@
         <v>144</v>
       </c>
       <c r="B69" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C69" t="s">
         <v>68</v>
@@ -3571,7 +3571,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C71" t="s">
         <v>68</v>
@@ -3731,7 +3731,7 @@
         <v>156</v>
       </c>
       <c r="B76" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C76" t="s">
         <v>68</v>
@@ -3795,7 +3795,7 @@
         <v>159</v>
       </c>
       <c r="B78" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C78" t="s">
         <v>68</v>
@@ -3827,7 +3827,7 @@
         <v>160</v>
       </c>
       <c r="B79" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C79" t="s">
         <v>68</v>
@@ -4071,7 +4071,7 @@
         <v>185</v>
       </c>
       <c r="B87" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C87" t="s">
         <v>175</v>
@@ -4100,7 +4100,7 @@
         <v>186</v>
       </c>
       <c r="B88" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C88" t="s">
         <v>175</v>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B761E4-7A32-477A-B922-D4DD6BD1716C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC1DF1A-62DB-4BC5-9E6B-5F09EB19BC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="311">
   <si>
     <t>variable</t>
   </si>
@@ -871,6 +871,9 @@
     <t>#FDE0DD,#FBB4B9,#F768A1,#C51B8A</t>
   </si>
   <si>
+    <t>#F2F2F7,#D9E0EE,#AEB8D0,#7A86A2</t>
+  </si>
+  <si>
     <t>#F4E6F8,#E0C2F0,#C08AE0,#8C4CB8</t>
   </si>
   <si>
@@ -953,27 +956,6 @@
   </si>
   <si>
     <t>Leg. Elections Concurrent with Nat. Elections</t>
-  </si>
-  <si>
-    <t>add_indices</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Higher values indicate cleaner elections at the subnational executive level, reflecting lower post-electoral conflict.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Higher values indicate higher levels of subnational legistlative competitiveness.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Higher values indicate higher levels of subnational executive competitiveness.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Higher values indicate higher levels of subnational democracy.</t>
-  </si>
-  <si>
-    <t>#C0D2EB,#4257A8</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Higher values indicate higher subnational executive turnover.</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.42578125" bestFit="1" customWidth="1"/>
@@ -1362,7 +1344,7 @@
     <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1393,16 +1375,13 @@
       <c r="J1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>267</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D2" t="s">
         <v>276</v>
@@ -1411,7 +1390,7 @@
         <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1425,11 +1404,8 @@
       <c r="J2" t="s">
         <v>273</v>
       </c>
-      <c r="K2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>268</v>
       </c>
@@ -1443,7 +1419,7 @@
         <v>121</v>
       </c>
       <c r="F3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1457,16 +1433,13 @@
       <c r="J3" t="s">
         <v>274</v>
       </c>
-      <c r="K3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>269</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D4" t="s">
         <v>276</v>
@@ -1475,7 +1448,7 @@
         <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1489,16 +1462,13 @@
       <c r="J4" t="s">
         <v>277</v>
       </c>
-      <c r="K4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>270</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D5" t="s">
         <v>276</v>
@@ -1507,7 +1477,7 @@
         <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1521,16 +1491,13 @@
       <c r="J5" t="s">
         <v>278</v>
       </c>
-      <c r="K5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>271</v>
       </c>
       <c r="B6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D6" t="s">
         <v>276</v>
@@ -1539,7 +1506,7 @@
         <v>121</v>
       </c>
       <c r="F6" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1553,16 +1520,13 @@
       <c r="J6" t="s">
         <v>279</v>
       </c>
-      <c r="K6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>272</v>
       </c>
       <c r="B7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D7" t="s">
         <v>276</v>
@@ -1585,11 +1549,8 @@
       <c r="J7" t="s">
         <v>280</v>
       </c>
-      <c r="K7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1618,7 +1579,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1647,7 +1608,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1676,7 +1637,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1705,7 +1666,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1734,7 +1695,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1766,7 +1727,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1795,7 +1756,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1827,7 +1788,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -2484,7 +2445,7 @@
         <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2492,7 +2453,7 @@
         <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C37" t="s">
         <v>68</v>
@@ -2524,7 +2485,7 @@
         <v>87</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C38" t="s">
         <v>21</v>
@@ -2556,7 +2517,7 @@
         <v>88</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C39" t="s">
         <v>21</v>
@@ -2713,7 +2674,7 @@
         <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C44" t="s">
         <v>68</v>
@@ -2777,7 +2738,7 @@
         <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C46" t="s">
         <v>68</v>
@@ -2841,7 +2802,7 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C48" t="s">
         <v>68</v>
@@ -2905,7 +2866,7 @@
         <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C50" t="s">
         <v>68</v>
@@ -2969,7 +2930,7 @@
         <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C52" t="s">
         <v>68</v>
@@ -3033,7 +2994,7 @@
         <v>115</v>
       </c>
       <c r="B54" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C54" t="s">
         <v>68</v>
@@ -3065,7 +3026,7 @@
         <v>116</v>
       </c>
       <c r="B55" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C55" t="s">
         <v>68</v>
@@ -3182,7 +3143,7 @@
         <v>22</v>
       </c>
       <c r="J58" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -3254,7 +3215,7 @@
         <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C61" t="s">
         <v>68</v>
@@ -3318,7 +3279,7 @@
         <v>133</v>
       </c>
       <c r="B63" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C63" t="s">
         <v>68</v>
@@ -3507,7 +3468,7 @@
         <v>144</v>
       </c>
       <c r="B69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C69" t="s">
         <v>68</v>
@@ -3571,7 +3532,7 @@
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C71" t="s">
         <v>68</v>
@@ -3731,7 +3692,7 @@
         <v>156</v>
       </c>
       <c r="B76" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C76" t="s">
         <v>68</v>
@@ -3795,7 +3756,7 @@
         <v>159</v>
       </c>
       <c r="B78" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C78" t="s">
         <v>68</v>
@@ -3827,7 +3788,7 @@
         <v>160</v>
       </c>
       <c r="B79" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C79" t="s">
         <v>68</v>
@@ -4071,7 +4032,7 @@
         <v>185</v>
       </c>
       <c r="B87" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C87" t="s">
         <v>175</v>
@@ -4100,7 +4061,7 @@
         <v>186</v>
       </c>
       <c r="B88" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C88" t="s">
         <v>175</v>

--- a/data/dict_new.xlsx
+++ b/data/dict_new.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pipei\OneDrive\Escritorio\subn_v3\subnational_gov\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B761E4-7A32-477A-B922-D4DD6BD1716C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715FB4AB-E1E0-4B53-B7F6-16EAA7744027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -460,9 +460,6 @@
     <t>margin_victory_sub_leg</t>
   </si>
   <si>
-    <t>cumulative_electoral_year_sub_leg</t>
-  </si>
-  <si>
     <t>Cumulative Elections Leg.</t>
   </si>
   <si>
@@ -974,6 +971,9 @@
   </si>
   <si>
     <t xml:space="preserve"> Higher values indicate higher subnational executive turnover.</t>
+  </si>
+  <si>
+    <t>cumulative_elections_year_sub_leg</t>
   </si>
 </sst>
 </file>
@@ -1045,12 +1045,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1391,27 +1394,27 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
         <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1423,27 +1426,27 @@
         <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" t="s">
         <v>275</v>
-      </c>
-      <c r="D3" t="s">
-        <v>276</v>
       </c>
       <c r="E3" t="s">
         <v>121</v>
       </c>
       <c r="F3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1455,27 +1458,27 @@
         <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E4" t="s">
         <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1487,27 +1490,27 @@
         <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E5" t="s">
         <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1519,59 +1522,59 @@
         <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E6" t="s">
         <v>121</v>
       </c>
       <c r="F6" t="s">
+        <v>314</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>278</v>
+      </c>
+      <c r="K6" t="s">
         <v>315</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" t="s">
-        <v>279</v>
-      </c>
-      <c r="K6" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E7" t="s">
         <v>121</v>
       </c>
       <c r="F7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1583,10 +1586,10 @@
         <v>22</v>
       </c>
       <c r="J7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1615,7 +1618,7 @@
         <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1644,7 +1647,7 @@
         <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1673,7 +1676,7 @@
         <v>22</v>
       </c>
       <c r="J10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1702,7 +1705,7 @@
         <v>22</v>
       </c>
       <c r="J11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1731,7 +1734,7 @@
         <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1763,7 +1766,7 @@
         <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1792,7 +1795,7 @@
         <v>14</v>
       </c>
       <c r="J14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1824,7 +1827,7 @@
         <v>14</v>
       </c>
       <c r="J15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1856,7 +1859,7 @@
         <v>14</v>
       </c>
       <c r="J16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1888,7 +1891,7 @@
         <v>14</v>
       </c>
       <c r="J17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1917,7 +1920,7 @@
         <v>14</v>
       </c>
       <c r="J18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1949,7 +1952,7 @@
         <v>14</v>
       </c>
       <c r="J19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1981,7 +1984,7 @@
         <v>14</v>
       </c>
       <c r="J20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2010,7 +2013,7 @@
         <v>22</v>
       </c>
       <c r="J21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2042,7 +2045,7 @@
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2071,7 +2074,7 @@
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2103,7 +2106,7 @@
         <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2135,7 +2138,7 @@
         <v>22</v>
       </c>
       <c r="J25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2167,7 +2170,7 @@
         <v>22</v>
       </c>
       <c r="J26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2199,7 +2202,7 @@
         <v>22</v>
       </c>
       <c r="J27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2231,7 +2234,7 @@
         <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2263,7 +2266,7 @@
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2292,7 +2295,7 @@
         <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2324,7 +2327,7 @@
         <v>22</v>
       </c>
       <c r="J31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2356,7 +2359,7 @@
         <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2388,7 +2391,7 @@
         <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2420,7 +2423,7 @@
         <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2452,7 +2455,7 @@
         <v>22</v>
       </c>
       <c r="J35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2484,7 +2487,7 @@
         <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2492,7 +2495,7 @@
         <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C37" t="s">
         <v>68</v>
@@ -2516,7 +2519,7 @@
         <v>22</v>
       </c>
       <c r="J37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2524,7 +2527,7 @@
         <v>87</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C38" t="s">
         <v>21</v>
@@ -2548,7 +2551,7 @@
         <v>22</v>
       </c>
       <c r="J38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2556,7 +2559,7 @@
         <v>88</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C39" t="s">
         <v>21</v>
@@ -2580,7 +2583,7 @@
         <v>22</v>
       </c>
       <c r="J39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2612,7 +2615,7 @@
         <v>22</v>
       </c>
       <c r="J40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2641,7 +2644,7 @@
         <v>22</v>
       </c>
       <c r="J41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2673,7 +2676,7 @@
         <v>22</v>
       </c>
       <c r="J42" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2705,7 +2708,7 @@
         <v>22</v>
       </c>
       <c r="J43" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2713,7 +2716,7 @@
         <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C44" t="s">
         <v>68</v>
@@ -2737,7 +2740,7 @@
         <v>22</v>
       </c>
       <c r="J44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -2769,7 +2772,7 @@
         <v>22</v>
       </c>
       <c r="J45" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2777,7 +2780,7 @@
         <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C46" t="s">
         <v>68</v>
@@ -2801,7 +2804,7 @@
         <v>22</v>
       </c>
       <c r="J46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2833,7 +2836,7 @@
         <v>22</v>
       </c>
       <c r="J47" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2841,7 +2844,7 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C48" t="s">
         <v>68</v>
@@ -2865,7 +2868,7 @@
         <v>22</v>
       </c>
       <c r="J48" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -2897,7 +2900,7 @@
         <v>22</v>
       </c>
       <c r="J49" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2905,7 +2908,7 @@
         <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C50" t="s">
         <v>68</v>
@@ -2929,7 +2932,7 @@
         <v>22</v>
       </c>
       <c r="J50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -2961,7 +2964,7 @@
         <v>22</v>
       </c>
       <c r="J51" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -2969,7 +2972,7 @@
         <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C52" t="s">
         <v>68</v>
@@ -2993,7 +2996,7 @@
         <v>22</v>
       </c>
       <c r="J52" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -3025,7 +3028,7 @@
         <v>22</v>
       </c>
       <c r="J53" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -3033,7 +3036,7 @@
         <v>115</v>
       </c>
       <c r="B54" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C54" t="s">
         <v>68</v>
@@ -3057,7 +3060,7 @@
         <v>22</v>
       </c>
       <c r="J54" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -3065,7 +3068,7 @@
         <v>116</v>
       </c>
       <c r="B55" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C55" t="s">
         <v>68</v>
@@ -3089,7 +3092,7 @@
         <v>22</v>
       </c>
       <c r="J55" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -3121,7 +3124,7 @@
         <v>22</v>
       </c>
       <c r="J56" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,18 +3153,18 @@
         <v>22</v>
       </c>
       <c r="J57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>178</v>
+      </c>
+      <c r="B58" t="s">
         <v>179</v>
       </c>
-      <c r="B58" t="s">
-        <v>180</v>
-      </c>
       <c r="C58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D58" t="s">
         <v>125</v>
@@ -3182,7 +3185,7 @@
         <v>22</v>
       </c>
       <c r="J58" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -3214,7 +3217,7 @@
         <v>22</v>
       </c>
       <c r="J59" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -3246,7 +3249,7 @@
         <v>22</v>
       </c>
       <c r="J60" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -3254,7 +3257,7 @@
         <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C61" t="s">
         <v>68</v>
@@ -3278,7 +3281,7 @@
         <v>22</v>
       </c>
       <c r="J61" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -3310,7 +3313,7 @@
         <v>22</v>
       </c>
       <c r="J62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -3318,7 +3321,7 @@
         <v>133</v>
       </c>
       <c r="B63" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C63" t="s">
         <v>68</v>
@@ -3342,7 +3345,7 @@
         <v>22</v>
       </c>
       <c r="J63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -3371,7 +3374,7 @@
         <v>22</v>
       </c>
       <c r="J64" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -3403,7 +3406,7 @@
         <v>22</v>
       </c>
       <c r="J65" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -3435,7 +3438,7 @@
         <v>22</v>
       </c>
       <c r="J66" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -3467,7 +3470,7 @@
         <v>22</v>
       </c>
       <c r="J67" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -3499,7 +3502,7 @@
         <v>22</v>
       </c>
       <c r="J68" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -3507,7 +3510,7 @@
         <v>144</v>
       </c>
       <c r="B69" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C69" t="s">
         <v>68</v>
@@ -3531,15 +3534,15 @@
         <v>22</v>
       </c>
       <c r="J69" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B70" t="s">
         <v>145</v>
-      </c>
-      <c r="B70" t="s">
-        <v>146</v>
       </c>
       <c r="C70" t="s">
         <v>68</v>
@@ -3563,15 +3566,15 @@
         <v>22</v>
       </c>
       <c r="J70" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B71" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C71" t="s">
         <v>68</v>
@@ -3595,15 +3598,15 @@
         <v>22</v>
       </c>
       <c r="J71" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>147</v>
+      </c>
+      <c r="B72" t="s">
         <v>148</v>
-      </c>
-      <c r="B72" t="s">
-        <v>149</v>
       </c>
       <c r="C72" t="s">
         <v>68</v>
@@ -3627,15 +3630,15 @@
         <v>22</v>
       </c>
       <c r="J72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>149</v>
+      </c>
+      <c r="B73" t="s">
         <v>150</v>
-      </c>
-      <c r="B73" t="s">
-        <v>151</v>
       </c>
       <c r="C73" t="s">
         <v>68</v>
@@ -3659,15 +3662,15 @@
         <v>22</v>
       </c>
       <c r="J73" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>151</v>
+      </c>
+      <c r="B74" t="s">
         <v>152</v>
-      </c>
-      <c r="B74" t="s">
-        <v>153</v>
       </c>
       <c r="C74" t="s">
         <v>68</v>
@@ -3691,15 +3694,15 @@
         <v>22</v>
       </c>
       <c r="J74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>153</v>
+      </c>
+      <c r="B75" t="s">
         <v>154</v>
-      </c>
-      <c r="B75" t="s">
-        <v>155</v>
       </c>
       <c r="C75" t="s">
         <v>68</v>
@@ -3723,15 +3726,15 @@
         <v>22</v>
       </c>
       <c r="J75" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B76" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C76" t="s">
         <v>68</v>
@@ -3755,15 +3758,15 @@
         <v>22</v>
       </c>
       <c r="J76" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" t="s">
         <v>157</v>
-      </c>
-      <c r="B77" t="s">
-        <v>158</v>
       </c>
       <c r="C77" t="s">
         <v>68</v>
@@ -3787,15 +3790,15 @@
         <v>22</v>
       </c>
       <c r="J77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B78" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C78" t="s">
         <v>68</v>
@@ -3819,15 +3822,15 @@
         <v>22</v>
       </c>
       <c r="J78" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B79" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C79" t="s">
         <v>68</v>
@@ -3836,11 +3839,11 @@
         <v>125</v>
       </c>
       <c r="E79" t="s">
+        <v>160</v>
+      </c>
+      <c r="F79" t="s">
         <v>161</v>
       </c>
-      <c r="F79" t="s">
-        <v>162</v>
-      </c>
       <c r="G79">
         <v>1</v>
       </c>
@@ -3851,15 +3854,15 @@
         <v>22</v>
       </c>
       <c r="J79" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>162</v>
+      </c>
+      <c r="B80" t="s">
         <v>163</v>
-      </c>
-      <c r="B80" t="s">
-        <v>164</v>
       </c>
       <c r="C80" t="s">
         <v>68</v>
@@ -3883,15 +3886,15 @@
         <v>22</v>
       </c>
       <c r="J80" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>164</v>
+      </c>
+      <c r="B81" t="s">
         <v>165</v>
-      </c>
-      <c r="B81" t="s">
-        <v>166</v>
       </c>
       <c r="C81" t="s">
         <v>68</v>
@@ -3900,11 +3903,11 @@
         <v>125</v>
       </c>
       <c r="E81" t="s">
+        <v>166</v>
+      </c>
+      <c r="F81" t="s">
         <v>167</v>
       </c>
-      <c r="F81" t="s">
-        <v>168</v>
-      </c>
       <c r="G81">
         <v>1</v>
       </c>
@@ -3915,15 +3918,15 @@
         <v>22</v>
       </c>
       <c r="J81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>168</v>
+      </c>
+      <c r="B82" t="s">
         <v>169</v>
-      </c>
-      <c r="B82" t="s">
-        <v>170</v>
       </c>
       <c r="C82" t="s">
         <v>68</v>
@@ -3932,11 +3935,11 @@
         <v>125</v>
       </c>
       <c r="E82" t="s">
+        <v>170</v>
+      </c>
+      <c r="F82" t="s">
         <v>171</v>
       </c>
-      <c r="F82" t="s">
-        <v>172</v>
-      </c>
       <c r="G82">
         <v>1</v>
       </c>
@@ -3947,24 +3950,24 @@
         <v>22</v>
       </c>
       <c r="J82" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>172</v>
+      </c>
+      <c r="B83" t="s">
         <v>173</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>174</v>
-      </c>
-      <c r="C83" t="s">
-        <v>175</v>
       </c>
       <c r="D83" t="s">
         <v>125</v>
       </c>
       <c r="E83" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -3976,24 +3979,24 @@
         <v>22</v>
       </c>
       <c r="J83" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>176</v>
+      </c>
+      <c r="B84" t="s">
         <v>177</v>
       </c>
-      <c r="B84" t="s">
-        <v>178</v>
-      </c>
       <c r="C84" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D84" t="s">
         <v>125</v>
       </c>
       <c r="E84" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -4005,24 +4008,24 @@
         <v>22</v>
       </c>
       <c r="J84" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>180</v>
+      </c>
+      <c r="B85" t="s">
         <v>181</v>
       </c>
-      <c r="B85" t="s">
-        <v>182</v>
-      </c>
       <c r="C85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D85" t="s">
         <v>125</v>
       </c>
       <c r="E85" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -4034,18 +4037,18 @@
         <v>22</v>
       </c>
       <c r="J85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>182</v>
+      </c>
+      <c r="B86" t="s">
         <v>183</v>
       </c>
-      <c r="B86" t="s">
-        <v>184</v>
-      </c>
       <c r="C86" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D86" t="s">
         <v>125</v>
@@ -4063,24 +4066,24 @@
         <v>22</v>
       </c>
       <c r="J86" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B87" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D87" t="s">
         <v>125</v>
       </c>
       <c r="E87" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -4092,24 +4095,24 @@
         <v>22</v>
       </c>
       <c r="J87" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D88" t="s">
         <v>125</v>
       </c>
       <c r="E88" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -4121,7 +4124,7 @@
         <v>22</v>
       </c>
       <c r="J88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
